--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE02225B-6FBF-1B4E-AE5C-9E1CE1B87D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32670B56-35C2-C644-8BD8-EE860DDD5C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="620" windowWidth="28820" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1020" yWindow="1040" windowWidth="14980" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -143,9 +143,6 @@
     <t>H260834D</t>
   </si>
   <si>
-    <t>h262353d</t>
-  </si>
-  <si>
     <t>H262353D</t>
   </si>
   <si>
@@ -435,6 +432,9 @@
   </si>
   <si>
     <t>H265403Y</t>
+  </si>
+  <si>
+    <t>Tepeya</t>
   </si>
 </sst>
 </file>
@@ -993,6 +993,9 @@
       <c r="D2" s="6">
         <v>0.89</v>
       </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
       <c r="G2">
         <v>0.33</v>
       </c>
@@ -1015,6 +1018,9 @@
       <c r="D3" s="6">
         <v>0.92</v>
       </c>
+      <c r="E3">
+        <v>0.86</v>
+      </c>
       <c r="G3">
         <v>0.64</v>
       </c>
@@ -1037,6 +1043,9 @@
       <c r="D4" s="6">
         <v>0.85</v>
       </c>
+      <c r="E4">
+        <v>0.86</v>
+      </c>
       <c r="G4">
         <v>0.34</v>
       </c>
@@ -1059,6 +1068,9 @@
       <c r="D5" s="6">
         <v>0.82</v>
       </c>
+      <c r="E5">
+        <v>0.86</v>
+      </c>
       <c r="G5">
         <v>0.61</v>
       </c>
@@ -1081,6 +1093,9 @@
       <c r="D6" s="6">
         <v>0.8</v>
       </c>
+      <c r="E6">
+        <v>0.86</v>
+      </c>
       <c r="G6">
         <v>0.31</v>
       </c>
@@ -1102,6 +1117,9 @@
       <c r="D7" s="6">
         <v>0.86</v>
       </c>
+      <c r="E7">
+        <v>0.79</v>
+      </c>
       <c r="G7">
         <v>0.37</v>
       </c>
@@ -1124,6 +1142,9 @@
       <c r="D8" s="6">
         <v>0.92</v>
       </c>
+      <c r="E8">
+        <v>0.93</v>
+      </c>
       <c r="G8">
         <v>0.43</v>
       </c>
@@ -1146,6 +1167,9 @@
       <c r="D9" s="6">
         <v>0.97</v>
       </c>
+      <c r="E9">
+        <v>0.96</v>
+      </c>
       <c r="G9">
         <v>0.49</v>
       </c>
@@ -1168,6 +1192,9 @@
       <c r="D10" s="6">
         <v>0.7</v>
       </c>
+      <c r="E10">
+        <v>0.86</v>
+      </c>
       <c r="G10">
         <v>0.69</v>
       </c>
@@ -1190,6 +1217,9 @@
       <c r="D11" s="6">
         <v>0.86</v>
       </c>
+      <c r="E11">
+        <v>0.93</v>
+      </c>
       <c r="G11">
         <v>0.45</v>
       </c>
@@ -1201,16 +1231,19 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="D12" s="6">
         <v>0.97</v>
+      </c>
+      <c r="E12">
+        <v>0.79</v>
       </c>
       <c r="G12">
         <v>0.61</v>
@@ -1223,16 +1256,19 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="D13" s="6">
         <v>0.86</v>
+      </c>
+      <c r="E13">
+        <v>0.79</v>
       </c>
       <c r="G13">
         <v>0.22</v>
@@ -1245,16 +1281,19 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="D14" s="6">
         <v>0.7</v>
+      </c>
+      <c r="E14">
+        <v>0.96</v>
       </c>
       <c r="G14">
         <v>0.82</v>
@@ -1267,16 +1306,19 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="D15" s="6">
         <v>0.75</v>
+      </c>
+      <c r="E15">
+        <v>0.93</v>
       </c>
       <c r="G15">
         <v>0.36</v>
@@ -1289,16 +1331,19 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>44</v>
       </c>
       <c r="D16" s="6">
         <v>0.92</v>
+      </c>
+      <c r="E16">
+        <v>0.86</v>
       </c>
       <c r="G16">
         <v>0.4</v>
@@ -1311,17 +1356,20 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="D17" s="6">
         <v>0.76</v>
       </c>
+      <c r="E17">
+        <v>0.79</v>
+      </c>
       <c r="G17">
         <v>0.33</v>
       </c>
@@ -1332,16 +1380,19 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="D18" s="6">
         <v>0.87</v>
+      </c>
+      <c r="E18">
+        <v>0.86</v>
       </c>
       <c r="G18">
         <v>0.49</v>
@@ -1354,17 +1405,20 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>50</v>
       </c>
       <c r="D19" s="6">
         <v>0.94</v>
       </c>
+      <c r="E19">
+        <v>0.89</v>
+      </c>
       <c r="G19">
         <v>0.34</v>
       </c>
@@ -1375,16 +1429,19 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="D20" s="6">
         <v>0.93</v>
+      </c>
+      <c r="E20">
+        <v>0.82</v>
       </c>
       <c r="G20">
         <v>0.56999999999999995</v>
@@ -1397,16 +1454,19 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="D21" s="6">
         <v>0.7</v>
+      </c>
+      <c r="E21">
+        <v>0.86</v>
       </c>
       <c r="G21">
         <v>0.46</v>
@@ -1419,17 +1479,20 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="D22" s="6">
         <v>0.85</v>
       </c>
+      <c r="E22">
+        <v>0.89</v>
+      </c>
       <c r="G22">
         <v>0.6</v>
       </c>
@@ -1440,16 +1503,19 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="D23" s="6">
         <v>0.73</v>
+      </c>
+      <c r="E23">
+        <v>0.82</v>
       </c>
       <c r="G23">
         <v>0.43</v>
@@ -1462,16 +1528,19 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="D24" s="6">
         <v>0.8</v>
+      </c>
+      <c r="E24">
+        <v>0.93</v>
       </c>
       <c r="G24">
         <v>0.51</v>
@@ -1484,16 +1553,19 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="D25" s="6">
         <v>0.9</v>
+      </c>
+      <c r="E25">
+        <v>0.89</v>
       </c>
       <c r="G25">
         <v>0.6</v>
@@ -1506,17 +1578,20 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="D26" s="6">
         <v>0.83</v>
       </c>
+      <c r="E26">
+        <v>0.86</v>
+      </c>
       <c r="G26">
         <v>0.61</v>
       </c>
@@ -1527,16 +1602,19 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="D27" s="6">
         <v>0.63</v>
+      </c>
+      <c r="E27">
+        <v>0.89</v>
       </c>
       <c r="G27">
         <v>0.33</v>
@@ -1549,16 +1627,19 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="D28" s="6">
         <v>0.9</v>
+      </c>
+      <c r="E28">
+        <v>0.93</v>
       </c>
       <c r="G28">
         <v>0.84</v>
@@ -1571,17 +1652,20 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="D29" s="6">
         <v>0.94</v>
       </c>
+      <c r="E29">
+        <v>0.96</v>
+      </c>
       <c r="G29">
         <v>0.6</v>
       </c>
@@ -1592,16 +1676,19 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="D30" s="6">
         <v>0.93</v>
+      </c>
+      <c r="E30">
+        <v>0.89</v>
       </c>
       <c r="G30">
         <v>0.46</v>
@@ -1614,16 +1701,19 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="D31" s="6">
         <v>0.86</v>
+      </c>
+      <c r="E31">
+        <v>0.79</v>
       </c>
       <c r="G31">
         <v>0.69</v>
@@ -1636,17 +1726,20 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="D32" s="6">
         <v>0.86</v>
       </c>
+      <c r="E32">
+        <v>0.89</v>
+      </c>
       <c r="G32">
         <v>0.84</v>
       </c>
@@ -1657,16 +1750,19 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="D33" s="6">
         <v>0.82</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
       </c>
       <c r="G33">
         <v>0.45</v>
@@ -1679,16 +1775,19 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="D34" s="6">
         <v>0.96</v>
+      </c>
+      <c r="E34">
+        <v>0.79</v>
       </c>
       <c r="G34">
         <v>0.66</v>
@@ -1701,17 +1800,20 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>82</v>
       </c>
       <c r="D35" s="6">
         <v>0.83</v>
       </c>
+      <c r="E35">
+        <v>0.89</v>
+      </c>
       <c r="G35">
         <v>0.25</v>
       </c>
@@ -1722,16 +1824,19 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>84</v>
       </c>
       <c r="D36" s="6">
         <v>0.89</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
       </c>
       <c r="G36">
         <v>0.24</v>
@@ -1744,17 +1849,20 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="6" t="s">
         <v>85</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>86</v>
       </c>
       <c r="D37" s="6">
         <v>0.82</v>
       </c>
+      <c r="E37">
+        <v>0.82</v>
+      </c>
       <c r="G37">
         <v>0.42</v>
       </c>
@@ -1765,16 +1873,19 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="D38" s="6">
         <v>0.83</v>
+      </c>
+      <c r="E38">
+        <v>0.79</v>
       </c>
       <c r="G38">
         <v>0.61</v>
@@ -1787,16 +1898,19 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="6" t="s">
         <v>89</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>90</v>
       </c>
       <c r="D39" s="6">
         <v>0.85</v>
+      </c>
+      <c r="E39">
+        <v>0.71</v>
       </c>
       <c r="G39">
         <v>0.45</v>
@@ -1815,10 +1929,13 @@
         <v>15</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D40" s="6">
         <v>0.89</v>
+      </c>
+      <c r="E40">
+        <v>0.93</v>
       </c>
       <c r="G40">
         <v>0.56000000000000005</v>
@@ -1831,16 +1948,19 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="6" t="s">
         <v>92</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>93</v>
       </c>
       <c r="D41" s="6">
         <v>0.86</v>
+      </c>
+      <c r="E41">
+        <v>0.79</v>
       </c>
       <c r="G41">
         <v>0.22</v>
@@ -1853,17 +1973,20 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="D42" s="6">
         <v>0.89</v>
       </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
       <c r="G42">
         <v>0.43</v>
       </c>
@@ -1874,16 +1997,19 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>97</v>
       </c>
       <c r="D43" s="6">
         <v>0.82</v>
+      </c>
+      <c r="E43">
+        <v>0.96</v>
       </c>
       <c r="G43">
         <v>0.6</v>
@@ -1896,16 +2022,19 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="D44" s="6">
         <v>0.8</v>
+      </c>
+      <c r="E44">
+        <v>0.93</v>
       </c>
       <c r="G44">
         <v>0.63</v>
@@ -1918,16 +2047,19 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="D45" s="6">
         <v>0.85</v>
+      </c>
+      <c r="E45">
+        <v>0.89</v>
       </c>
       <c r="G45">
         <v>0.63</v>
@@ -1940,16 +2072,19 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="D46" s="6">
         <v>0.89</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
       </c>
       <c r="G46">
         <v>0.46</v>
@@ -1962,16 +2097,19 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>104</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>105</v>
       </c>
       <c r="D47" s="6">
         <v>0.73</v>
+      </c>
+      <c r="E47">
+        <v>0.89</v>
       </c>
       <c r="G47">
         <v>0.45</v>
@@ -1984,17 +2122,20 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="C48" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>108</v>
       </c>
       <c r="D48" s="6">
         <v>0.9</v>
       </c>
+      <c r="E48">
+        <v>0.89</v>
+      </c>
       <c r="G48">
         <v>0.49</v>
       </c>
@@ -2005,17 +2146,20 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="D49" s="6">
         <v>0.83</v>
       </c>
+      <c r="E49">
+        <v>0.86</v>
+      </c>
       <c r="G49">
         <v>0.46</v>
       </c>
@@ -2026,17 +2170,20 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C50" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="D50" s="6">
         <v>0.85</v>
       </c>
+      <c r="E50">
+        <v>0.93</v>
+      </c>
       <c r="G50">
         <v>0.43</v>
       </c>
@@ -2047,16 +2194,19 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C51" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="D51" s="6">
         <v>0.7</v>
+      </c>
+      <c r="E51">
+        <v>0.89</v>
       </c>
       <c r="G51">
         <v>0.34</v>
@@ -2069,16 +2219,19 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C52" s="6" t="s">
         <v>115</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>116</v>
       </c>
       <c r="D52" s="6">
         <v>0.76</v>
+      </c>
+      <c r="E52">
+        <v>0.79</v>
       </c>
       <c r="G52">
         <v>0.61</v>
@@ -2091,16 +2244,19 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C53" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="D53" s="6">
         <v>0.9</v>
+      </c>
+      <c r="E53">
+        <v>0.89</v>
       </c>
       <c r="G53">
         <v>0.51</v>
@@ -2113,17 +2269,20 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="D54" s="6">
         <v>0.75</v>
       </c>
+      <c r="E54">
+        <v>0.89</v>
+      </c>
       <c r="G54">
         <v>0.49</v>
       </c>
@@ -2134,16 +2293,19 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="D55" s="6">
         <v>0.69</v>
+      </c>
+      <c r="E55">
+        <v>0.79</v>
       </c>
       <c r="G55">
         <v>0.45</v>
@@ -2156,16 +2318,19 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="D56" s="6">
         <v>0.18</v>
+      </c>
+      <c r="E56">
+        <v>0.96</v>
       </c>
       <c r="G56">
         <v>0.28000000000000003</v>
@@ -2178,17 +2343,20 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="D57" s="6">
         <v>0.72</v>
       </c>
+      <c r="E57">
+        <v>0.64</v>
+      </c>
       <c r="G57">
         <v>0</v>
       </c>
@@ -2199,16 +2367,19 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="D58" s="6">
         <v>0.77</v>
+      </c>
+      <c r="E58">
+        <v>0.89</v>
       </c>
       <c r="G58">
         <v>0.57999999999999996</v>
@@ -2221,16 +2392,19 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C59" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>130</v>
       </c>
       <c r="D59" s="6">
         <v>0.92</v>
+      </c>
+      <c r="E59">
+        <v>0.79</v>
       </c>
       <c r="G59">
         <v>0.52</v>
@@ -2243,16 +2417,19 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C60" s="6" t="s">
         <v>131</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>132</v>
       </c>
       <c r="D60" s="6">
         <v>0.66</v>
+      </c>
+      <c r="E60">
+        <v>0.96</v>
       </c>
       <c r="G60">
         <v>0.43</v>

--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32670B56-35C2-C644-8BD8-EE860DDD5C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1A1228-FB41-4246-AB49-FAB9824B8B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="1040" windowWidth="14980" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -593,7 +593,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}" name="Table1" displayName="Table1" ref="A1:M228" totalsRowShown="0">
   <autoFilter ref="A1:M228" xr:uid="{16CEB027-FB46-1A44-BA46-BD4AD30C864F}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M228">
-    <sortCondition ref="C1:C228"/>
+    <sortCondition ref="B1:B228"/>
   </sortState>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
@@ -1231,22 +1231,22 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="6" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D12" s="6">
-        <v>0.97</v>
+        <v>0.86</v>
       </c>
       <c r="E12">
         <v>0.79</v>
       </c>
       <c r="G12">
-        <v>0.61</v>
+        <v>0.22</v>
       </c>
       <c r="H12" s="3"/>
       <c r="J12">
@@ -1256,22 +1256,22 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13" s="6">
-        <v>0.86</v>
+        <v>0.7</v>
       </c>
       <c r="E13">
-        <v>0.79</v>
+        <v>0.96</v>
       </c>
       <c r="G13">
-        <v>0.22</v>
+        <v>0.82</v>
       </c>
       <c r="H13" s="3"/>
       <c r="J13">
@@ -1281,22 +1281,22 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D14" s="6">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="E14">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="G14">
-        <v>0.82</v>
+        <v>0.36</v>
       </c>
       <c r="H14" s="3"/>
       <c r="J14">
@@ -1306,122 +1306,122 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D15" s="6">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="E15">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="G15">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="H15" s="3"/>
       <c r="J15">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M15" s="4"/>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D16" s="6">
-        <v>0.92</v>
+        <v>0.76</v>
       </c>
       <c r="E16">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="G16">
-        <v>0.4</v>
-      </c>
-      <c r="H16" s="3"/>
+        <v>0.33</v>
+      </c>
       <c r="J16">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="M16" s="4"/>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D17" s="6">
-        <v>0.76</v>
+        <v>0.87</v>
       </c>
       <c r="E17">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="G17">
-        <v>0.33</v>
-      </c>
+        <v>0.49</v>
+      </c>
+      <c r="H17" s="3"/>
       <c r="J17">
-        <v>0.6</v>
+        <v>0.25</v>
       </c>
       <c r="M17" s="4"/>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D18" s="6">
-        <v>0.87</v>
+        <v>0.94</v>
       </c>
       <c r="E18">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="G18">
-        <v>0.49</v>
-      </c>
-      <c r="H18" s="3"/>
+        <v>0.34</v>
+      </c>
       <c r="J18">
-        <v>0.25</v>
+        <v>0.79</v>
       </c>
       <c r="M18" s="4"/>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D19" s="6">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="E19">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="G19">
-        <v>0.34</v>
-      </c>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H19" s="3"/>
       <c r="J19">
         <v>0.79</v>
       </c>
@@ -1429,73 +1429,73 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D20" s="6">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="E20">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="G20">
-        <v>0.56999999999999995</v>
+        <v>0.46</v>
       </c>
       <c r="H20" s="3"/>
       <c r="J20">
-        <v>0.79</v>
+        <v>0.6</v>
       </c>
       <c r="M20" s="4"/>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D21" s="6">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="E21">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="G21">
-        <v>0.46</v>
-      </c>
-      <c r="H21" s="3"/>
+        <v>0.6</v>
+      </c>
       <c r="J21">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="M21" s="4"/>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D22" s="6">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="E22">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="G22">
-        <v>0.6</v>
-      </c>
+        <v>0.43</v>
+      </c>
+      <c r="H22" s="3"/>
       <c r="J22">
         <v>0.79</v>
       </c>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D23" s="6">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="E23">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="G23">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="H23" s="3"/>
       <c r="J23">
@@ -1528,147 +1528,147 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D24" s="6">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E24">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="G24">
-        <v>0.51</v>
+        <v>0.6</v>
       </c>
       <c r="H24" s="3"/>
       <c r="J24">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="M24" s="4"/>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D25" s="6">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="E25">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="G25">
-        <v>0.6</v>
-      </c>
-      <c r="H25" s="3"/>
+        <v>0.61</v>
+      </c>
       <c r="J25">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="M25" s="4"/>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D26" s="6">
-        <v>0.83</v>
+        <v>0.63</v>
       </c>
       <c r="E26">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="G26">
-        <v>0.61</v>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="H26" s="3"/>
       <c r="J26">
         <v>0.79</v>
       </c>
-      <c r="M26" s="4"/>
+      <c r="M26" s="8"/>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D27" s="6">
-        <v>0.63</v>
+        <v>0.9</v>
       </c>
       <c r="E27">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="G27">
-        <v>0.33</v>
+        <v>0.84</v>
       </c>
       <c r="H27" s="3"/>
       <c r="J27">
-        <v>0.79</v>
-      </c>
-      <c r="M27" s="8"/>
+        <v>0.74</v>
+      </c>
+      <c r="M27" s="4"/>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D28" s="6">
-        <v>0.9</v>
+        <v>0.94</v>
       </c>
       <c r="E28">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="G28">
-        <v>0.84</v>
-      </c>
-      <c r="H28" s="3"/>
+        <v>0.6</v>
+      </c>
       <c r="J28">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="M28" s="4"/>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D29" s="6">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="E29">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="G29">
-        <v>0.6</v>
-      </c>
+        <v>0.46</v>
+      </c>
+      <c r="H29" s="3"/>
       <c r="J29">
         <v>0.79</v>
       </c>
@@ -1676,219 +1676,219 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D30" s="6">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="E30">
-        <v>0.89</v>
+        <v>0.79</v>
       </c>
       <c r="G30">
-        <v>0.46</v>
+        <v>0.69</v>
       </c>
       <c r="H30" s="3"/>
       <c r="J30">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="M30" s="4"/>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D31" s="6">
         <v>0.86</v>
       </c>
       <c r="E31">
-        <v>0.79</v>
+        <v>0.89</v>
       </c>
       <c r="G31">
-        <v>0.69</v>
-      </c>
-      <c r="H31" s="3"/>
+        <v>0.84</v>
+      </c>
       <c r="J31">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="M31" s="4"/>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D32" s="6">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="E32">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>0.84</v>
-      </c>
+        <v>0.45</v>
+      </c>
+      <c r="H32" s="3"/>
       <c r="J32">
-        <v>0.74</v>
-      </c>
-      <c r="M32" s="4"/>
+        <v>0.77</v>
+      </c>
+      <c r="M32" s="8"/>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D33" s="6">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="G33">
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
       <c r="H33" s="3"/>
       <c r="J33">
-        <v>0.77</v>
-      </c>
-      <c r="M33" s="8"/>
+        <v>0.71</v>
+      </c>
+      <c r="M33" s="4"/>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D34" s="6">
-        <v>0.96</v>
+        <v>0.83</v>
       </c>
       <c r="E34">
-        <v>0.79</v>
+        <v>0.89</v>
       </c>
       <c r="G34">
-        <v>0.66</v>
-      </c>
-      <c r="H34" s="3"/>
+        <v>0.25</v>
+      </c>
       <c r="J34">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="M34" s="4"/>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D35" s="6">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="E35">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>0.25</v>
-      </c>
+        <v>0.24</v>
+      </c>
+      <c r="H35" s="3"/>
       <c r="J35">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="M35" s="4"/>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D36" s="6">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="G36">
-        <v>0.24</v>
-      </c>
-      <c r="H36" s="3"/>
+        <v>0.42</v>
+      </c>
       <c r="J36">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="M36" s="4"/>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D37" s="6">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="E37">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="G37">
-        <v>0.42</v>
-      </c>
+        <v>0.61</v>
+      </c>
+      <c r="H37" s="3"/>
       <c r="J37">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D38" s="6">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="E38">
-        <v>0.79</v>
+        <v>0.71</v>
       </c>
       <c r="G38">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="H38" s="3"/>
       <c r="J38">
@@ -1898,171 +1898,171 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="6" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D39" s="6">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="E39">
-        <v>0.71</v>
+        <v>0.93</v>
       </c>
       <c r="G39">
-        <v>0.45</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H39" s="3"/>
       <c r="J39">
-        <v>0.77</v>
+        <v>0.6</v>
       </c>
       <c r="M39" s="4"/>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="6" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D40" s="6">
-        <v>0.89</v>
+        <v>0.86</v>
       </c>
       <c r="E40">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="G40">
-        <v>0.56000000000000005</v>
+        <v>0.22</v>
       </c>
       <c r="H40" s="3"/>
       <c r="J40">
-        <v>0.6</v>
+        <v>0.77</v>
       </c>
       <c r="M40" s="4"/>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D41" s="6">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="E41">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>0.22</v>
-      </c>
-      <c r="H41" s="3"/>
+        <v>0.43</v>
+      </c>
       <c r="J41">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="M41" s="4"/>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D42" s="6">
-        <v>0.89</v>
+        <v>0.82</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="G42">
-        <v>0.43</v>
-      </c>
+        <v>0.6</v>
+      </c>
+      <c r="H42" s="3"/>
       <c r="J42">
-        <v>0.71</v>
-      </c>
-      <c r="M42" s="4"/>
+        <v>0.77</v>
+      </c>
+      <c r="M42" s="8"/>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D43" s="6">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="E43">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="G43">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="H43" s="3"/>
       <c r="J43">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="M43" s="8"/>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D44" s="6">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="E44">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="G44">
         <v>0.63</v>
       </c>
       <c r="H44" s="3"/>
       <c r="J44">
-        <v>0.71</v>
-      </c>
-      <c r="M44" s="8"/>
+        <v>0.79</v>
+      </c>
+      <c r="M44" s="4"/>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D45" s="6">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="E45">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="H45" s="3"/>
       <c r="J45">
@@ -2072,26 +2072,26 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="6" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="D46" s="6">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="G46">
-        <v>0.46</v>
+        <v>0.61</v>
       </c>
       <c r="H46" s="3"/>
       <c r="J46">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="M46" s="4"/>
     </row>

--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D1A1228-FB41-4246-AB49-FAB9824B8B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CAFB5A-4D4F-3E4F-BBA9-E4D77C21C92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="1040" windowWidth="14980" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>

--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18CAFB5A-4D4F-3E4F-BBA9-E4D77C21C92B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7C46E8-9009-8842-B35D-375AC074E60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="1040" windowWidth="14980" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -531,7 +531,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -546,6 +546,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -999,7 +1002,9 @@
       <c r="G2">
         <v>0.33</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="9">
+        <v>0.77</v>
+      </c>
       <c r="J2">
         <v>0.6</v>
       </c>
@@ -1024,7 +1029,9 @@
       <c r="G3">
         <v>0.64</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="9">
+        <v>0.73</v>
+      </c>
       <c r="J3">
         <v>0.25</v>
       </c>
@@ -1049,7 +1056,9 @@
       <c r="G4">
         <v>0.34</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="9">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="J4">
         <v>0</v>
       </c>
@@ -1074,7 +1083,9 @@
       <c r="G5">
         <v>0.61</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="9">
+        <v>0.81</v>
+      </c>
       <c r="J5">
         <v>0.79</v>
       </c>
@@ -1099,6 +1110,9 @@
       <c r="G6">
         <v>0.31</v>
       </c>
+      <c r="H6" s="9">
+        <v>0.63</v>
+      </c>
       <c r="J6">
         <v>0.77</v>
       </c>
@@ -1123,7 +1137,9 @@
       <c r="G7">
         <v>0.37</v>
       </c>
-      <c r="H7" s="3"/>
+      <c r="H7" s="9">
+        <v>0.79</v>
+      </c>
       <c r="J7">
         <v>0.6</v>
       </c>
@@ -1148,7 +1164,9 @@
       <c r="G8">
         <v>0.43</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="H8" s="9">
+        <v>0.83</v>
+      </c>
       <c r="J8">
         <v>0.79</v>
       </c>
@@ -1173,7 +1191,9 @@
       <c r="G9">
         <v>0.49</v>
       </c>
-      <c r="H9" s="3"/>
+      <c r="H9" s="9">
+        <v>0.65</v>
+      </c>
       <c r="J9">
         <v>0.25</v>
       </c>
@@ -1198,7 +1218,9 @@
       <c r="G10">
         <v>0.69</v>
       </c>
-      <c r="H10" s="3"/>
+      <c r="H10" s="9">
+        <v>0.75</v>
+      </c>
       <c r="J10">
         <v>0</v>
       </c>
@@ -1223,7 +1245,9 @@
       <c r="G11">
         <v>0.45</v>
       </c>
-      <c r="H11" s="3"/>
+      <c r="H11" s="9">
+        <v>0.85</v>
+      </c>
       <c r="J11">
         <v>0.77</v>
       </c>
@@ -1248,7 +1272,9 @@
       <c r="G12">
         <v>0.22</v>
       </c>
-      <c r="H12" s="3"/>
+      <c r="H12" s="9">
+        <v>0.85</v>
+      </c>
       <c r="J12">
         <v>0</v>
       </c>
@@ -1273,7 +1299,9 @@
       <c r="G13">
         <v>0.82</v>
       </c>
-      <c r="H13" s="3"/>
+      <c r="H13" s="9">
+        <v>0.96</v>
+      </c>
       <c r="J13">
         <v>0</v>
       </c>
@@ -1298,7 +1326,9 @@
       <c r="G14">
         <v>0.36</v>
       </c>
-      <c r="H14" s="3"/>
+      <c r="H14" s="9">
+        <v>0.9</v>
+      </c>
       <c r="J14">
         <v>0</v>
       </c>
@@ -1323,7 +1353,9 @@
       <c r="G15">
         <v>0.4</v>
       </c>
-      <c r="H15" s="3"/>
+      <c r="H15" s="9">
+        <v>0.94</v>
+      </c>
       <c r="J15">
         <v>0.25</v>
       </c>
@@ -1348,6 +1380,9 @@
       <c r="G16">
         <v>0.33</v>
       </c>
+      <c r="H16" s="9">
+        <v>0.71</v>
+      </c>
       <c r="J16">
         <v>0.6</v>
       </c>
@@ -1372,7 +1407,9 @@
       <c r="G17">
         <v>0.49</v>
       </c>
-      <c r="H17" s="3"/>
+      <c r="H17" s="9">
+        <v>0.83</v>
+      </c>
       <c r="J17">
         <v>0.25</v>
       </c>
@@ -1397,6 +1434,9 @@
       <c r="G18">
         <v>0.34</v>
       </c>
+      <c r="H18" s="9">
+        <v>0.91</v>
+      </c>
       <c r="J18">
         <v>0.79</v>
       </c>
@@ -1421,7 +1461,9 @@
       <c r="G19">
         <v>0.56999999999999995</v>
       </c>
-      <c r="H19" s="3"/>
+      <c r="H19" s="9">
+        <v>0.69</v>
+      </c>
       <c r="J19">
         <v>0.79</v>
       </c>
@@ -1446,7 +1488,9 @@
       <c r="G20">
         <v>0.46</v>
       </c>
-      <c r="H20" s="3"/>
+      <c r="H20" s="9">
+        <v>0.79</v>
+      </c>
       <c r="J20">
         <v>0.6</v>
       </c>
@@ -1471,6 +1515,9 @@
       <c r="G21">
         <v>0.6</v>
       </c>
+      <c r="H21" s="9">
+        <v>0.9</v>
+      </c>
       <c r="J21">
         <v>0.79</v>
       </c>
@@ -1495,7 +1542,9 @@
       <c r="G22">
         <v>0.43</v>
       </c>
-      <c r="H22" s="3"/>
+      <c r="H22" s="9">
+        <v>0.83</v>
+      </c>
       <c r="J22">
         <v>0.79</v>
       </c>
@@ -1520,7 +1569,9 @@
       <c r="G23">
         <v>0.51</v>
       </c>
-      <c r="H23" s="3"/>
+      <c r="H23" s="9">
+        <v>0.88</v>
+      </c>
       <c r="J23">
         <v>0.79</v>
       </c>
@@ -1545,7 +1596,9 @@
       <c r="G24">
         <v>0.6</v>
       </c>
-      <c r="H24" s="3"/>
+      <c r="H24" s="9">
+        <v>0.71</v>
+      </c>
       <c r="J24">
         <v>0.77</v>
       </c>
@@ -1570,6 +1623,9 @@
       <c r="G25">
         <v>0.61</v>
       </c>
+      <c r="H25" s="9">
+        <v>0.88</v>
+      </c>
       <c r="J25">
         <v>0.79</v>
       </c>
@@ -1594,7 +1650,9 @@
       <c r="G26">
         <v>0.33</v>
       </c>
-      <c r="H26" s="3"/>
+      <c r="H26" s="9">
+        <v>0.77</v>
+      </c>
       <c r="J26">
         <v>0.79</v>
       </c>
@@ -1619,7 +1677,9 @@
       <c r="G27">
         <v>0.84</v>
       </c>
-      <c r="H27" s="3"/>
+      <c r="H27" s="9">
+        <v>0.65</v>
+      </c>
       <c r="J27">
         <v>0.74</v>
       </c>
@@ -1644,6 +1704,9 @@
       <c r="G28">
         <v>0.6</v>
       </c>
+      <c r="H28" s="9">
+        <v>0.88</v>
+      </c>
       <c r="J28">
         <v>0.79</v>
       </c>
@@ -1668,7 +1731,9 @@
       <c r="G29">
         <v>0.46</v>
       </c>
-      <c r="H29" s="3"/>
+      <c r="H29" s="9">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="J29">
         <v>0.79</v>
       </c>
@@ -1693,7 +1758,9 @@
       <c r="G30">
         <v>0.69</v>
       </c>
-      <c r="H30" s="3"/>
+      <c r="H30" s="9">
+        <v>0.88</v>
+      </c>
       <c r="J30">
         <v>0.77</v>
       </c>
@@ -1718,6 +1785,9 @@
       <c r="G31">
         <v>0.84</v>
       </c>
+      <c r="H31" s="9">
+        <v>0.88</v>
+      </c>
       <c r="J31">
         <v>0.74</v>
       </c>
@@ -1742,7 +1812,9 @@
       <c r="G32">
         <v>0.45</v>
       </c>
-      <c r="H32" s="3"/>
+      <c r="H32" s="9">
+        <v>0.67</v>
+      </c>
       <c r="J32">
         <v>0.77</v>
       </c>
@@ -1767,7 +1839,9 @@
       <c r="G33">
         <v>0.66</v>
       </c>
-      <c r="H33" s="3"/>
+      <c r="H33" s="9">
+        <v>0.56000000000000005</v>
+      </c>
       <c r="J33">
         <v>0.71</v>
       </c>
@@ -1792,6 +1866,9 @@
       <c r="G34">
         <v>0.25</v>
       </c>
+      <c r="H34" s="9">
+        <v>0.79</v>
+      </c>
       <c r="J34">
         <v>0.74</v>
       </c>
@@ -1816,7 +1893,9 @@
       <c r="G35">
         <v>0.24</v>
       </c>
-      <c r="H35" s="3"/>
+      <c r="H35" s="9">
+        <v>0.77</v>
+      </c>
       <c r="J35">
         <v>0.71</v>
       </c>
@@ -1841,6 +1920,9 @@
       <c r="G36">
         <v>0.42</v>
       </c>
+      <c r="H36" s="9">
+        <v>0.63</v>
+      </c>
       <c r="J36">
         <v>0.79</v>
       </c>
@@ -1865,7 +1947,9 @@
       <c r="G37">
         <v>0.61</v>
       </c>
-      <c r="H37" s="3"/>
+      <c r="H37" s="9">
+        <v>0.79</v>
+      </c>
       <c r="J37">
         <v>0.77</v>
       </c>
@@ -1890,7 +1974,9 @@
       <c r="G38">
         <v>0.45</v>
       </c>
-      <c r="H38" s="3"/>
+      <c r="H38" s="9">
+        <v>0.71</v>
+      </c>
       <c r="J38">
         <v>0.77</v>
       </c>
@@ -1915,7 +2001,9 @@
       <c r="G39">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H39" s="3"/>
+      <c r="H39" s="9">
+        <v>0.77</v>
+      </c>
       <c r="J39">
         <v>0.6</v>
       </c>
@@ -1940,7 +2028,9 @@
       <c r="G40">
         <v>0.22</v>
       </c>
-      <c r="H40" s="3"/>
+      <c r="H40" s="9">
+        <v>0.69</v>
+      </c>
       <c r="J40">
         <v>0.77</v>
       </c>
@@ -1965,6 +2055,9 @@
       <c r="G41">
         <v>0.43</v>
       </c>
+      <c r="H41" s="9">
+        <v>0.63</v>
+      </c>
       <c r="J41">
         <v>0.71</v>
       </c>
@@ -1989,7 +2082,9 @@
       <c r="G42">
         <v>0.6</v>
       </c>
-      <c r="H42" s="3"/>
+      <c r="H42" s="9">
+        <v>0.9</v>
+      </c>
       <c r="J42">
         <v>0.77</v>
       </c>
@@ -2014,7 +2109,9 @@
       <c r="G43">
         <v>0.63</v>
       </c>
-      <c r="H43" s="3"/>
+      <c r="H43" s="9">
+        <v>0.9</v>
+      </c>
       <c r="J43">
         <v>0.71</v>
       </c>
@@ -2039,7 +2136,9 @@
       <c r="G44">
         <v>0.63</v>
       </c>
-      <c r="H44" s="3"/>
+      <c r="H44" s="9">
+        <v>0.85</v>
+      </c>
       <c r="J44">
         <v>0.79</v>
       </c>
@@ -2064,7 +2163,9 @@
       <c r="G45">
         <v>0.46</v>
       </c>
-      <c r="H45" s="3"/>
+      <c r="H45" s="9">
+        <v>0.79</v>
+      </c>
       <c r="J45">
         <v>0.79</v>
       </c>
@@ -2089,7 +2190,9 @@
       <c r="G46">
         <v>0.61</v>
       </c>
-      <c r="H46" s="3"/>
+      <c r="H46" s="9">
+        <v>0.81</v>
+      </c>
       <c r="J46">
         <v>0</v>
       </c>
@@ -2114,7 +2217,9 @@
       <c r="G47">
         <v>0.45</v>
       </c>
-      <c r="H47" s="3"/>
+      <c r="H47" s="9">
+        <v>0.94</v>
+      </c>
       <c r="J47">
         <v>0.74</v>
       </c>
@@ -2139,6 +2244,9 @@
       <c r="G48">
         <v>0.49</v>
       </c>
+      <c r="H48" s="9">
+        <v>0.81</v>
+      </c>
       <c r="J48">
         <v>0.73</v>
       </c>
@@ -2163,6 +2271,9 @@
       <c r="G49">
         <v>0.46</v>
       </c>
+      <c r="H49" s="9">
+        <v>0.65</v>
+      </c>
       <c r="J49">
         <v>0.77</v>
       </c>
@@ -2187,6 +2298,9 @@
       <c r="G50">
         <v>0.43</v>
       </c>
+      <c r="H50" s="9">
+        <v>0.48</v>
+      </c>
       <c r="J50">
         <v>0.73</v>
       </c>
@@ -2211,7 +2325,9 @@
       <c r="G51">
         <v>0.34</v>
       </c>
-      <c r="H51" s="3"/>
+      <c r="H51" s="9">
+        <v>0.68</v>
+      </c>
       <c r="J51">
         <v>0.74</v>
       </c>
@@ -2236,7 +2352,9 @@
       <c r="G52">
         <v>0.61</v>
       </c>
-      <c r="H52" s="3"/>
+      <c r="H52" s="9">
+        <v>0.67</v>
+      </c>
       <c r="J52">
         <v>0.74</v>
       </c>
@@ -2261,7 +2379,9 @@
       <c r="G53">
         <v>0.51</v>
       </c>
-      <c r="H53" s="3"/>
+      <c r="H53" s="9">
+        <v>0.83</v>
+      </c>
       <c r="J53">
         <v>0.77</v>
       </c>
@@ -2286,6 +2406,9 @@
       <c r="G54">
         <v>0.49</v>
       </c>
+      <c r="H54" s="9">
+        <v>0.71</v>
+      </c>
       <c r="J54">
         <v>0.73</v>
       </c>
@@ -2310,7 +2433,9 @@
       <c r="G55">
         <v>0.45</v>
       </c>
-      <c r="H55" s="3"/>
+      <c r="H55" s="9">
+        <v>0.67</v>
+      </c>
       <c r="J55">
         <v>0.74</v>
       </c>
@@ -2335,7 +2460,9 @@
       <c r="G56">
         <v>0.28000000000000003</v>
       </c>
-      <c r="H56" s="3"/>
+      <c r="H56" s="9">
+        <v>0.73</v>
+      </c>
       <c r="J56">
         <v>0.73</v>
       </c>
@@ -2360,6 +2487,9 @@
       <c r="G57">
         <v>0</v>
       </c>
+      <c r="H57" s="9">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="J57">
         <v>0.73</v>
       </c>
@@ -2384,7 +2514,9 @@
       <c r="G58">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H58" s="3"/>
+      <c r="H58" s="9">
+        <v>0.65</v>
+      </c>
       <c r="J58">
         <v>0.73</v>
       </c>
@@ -2409,7 +2541,9 @@
       <c r="G59">
         <v>0.52</v>
       </c>
-      <c r="H59" s="3"/>
+      <c r="H59" s="9">
+        <v>0.69</v>
+      </c>
       <c r="J59">
         <v>0.77</v>
       </c>
@@ -2434,7 +2568,9 @@
       <c r="G60">
         <v>0.43</v>
       </c>
-      <c r="H60" s="3"/>
+      <c r="H60" s="9">
+        <v>0.57999999999999996</v>
+      </c>
       <c r="J60">
         <v>0.73</v>
       </c>

--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7C46E8-9009-8842-B35D-375AC074E60D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60E17AB-ADA3-B549-BAA4-8BE96215C372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="1040" windowWidth="14980" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1020" yWindow="1040" windowWidth="18500" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1297,7 +1297,7 @@
         <v>0.96</v>
       </c>
       <c r="G13">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="H13" s="9">
         <v>0.96</v>
@@ -1354,7 +1354,7 @@
         <v>0.4</v>
       </c>
       <c r="H15" s="9">
-        <v>0.94</v>
+        <v>1</v>
       </c>
       <c r="J15">
         <v>0.25</v>
@@ -1408,7 +1408,7 @@
         <v>0.49</v>
       </c>
       <c r="H17" s="9">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="J17">
         <v>0.25</v>
@@ -1462,7 +1462,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="H19" s="9">
-        <v>0.69</v>
+        <v>0.73</v>
       </c>
       <c r="J19">
         <v>0.79</v>

--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A60E17AB-ADA3-B549-BAA4-8BE96215C372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBED182B-49B7-074F-88AE-BE384FC3EA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="1040" windowWidth="18500" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>

--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBED182B-49B7-074F-88AE-BE384FC3EA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFA0094-EA63-4741-BD53-625E430DCD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="1040" windowWidth="18500" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -1543,7 +1543,7 @@
         <v>0.43</v>
       </c>
       <c r="H22" s="9">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="J22">
         <v>0.79</v>

--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CFA0094-EA63-4741-BD53-625E430DCD03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30662BAF-8D1E-5B4A-ACCC-841838B1E197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="1040" windowWidth="18500" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1020" yWindow="1040" windowWidth="24360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1006,7 +1006,7 @@
         <v>0.77</v>
       </c>
       <c r="J2">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="M2" s="7"/>
     </row>
@@ -1141,7 +1141,7 @@
         <v>0.79</v>
       </c>
       <c r="J7">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="M7" s="4"/>
     </row>
@@ -1384,7 +1384,7 @@
         <v>0.71</v>
       </c>
       <c r="J16">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="M16" s="4"/>
     </row>
@@ -1492,7 +1492,7 @@
         <v>0.79</v>
       </c>
       <c r="J20">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="M20" s="4"/>
     </row>
@@ -2005,7 +2005,7 @@
         <v>0.77</v>
       </c>
       <c r="J39">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="M39" s="4"/>
     </row>

--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30662BAF-8D1E-5B4A-ACCC-841838B1E197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80BC94C-E2D0-CD43-8CB0-D219096AEF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="1040" windowWidth="24360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
+    <workbookView xWindow="1020" yWindow="1040" windowWidth="26940" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -999,11 +999,17 @@
       <c r="E2">
         <v>1</v>
       </c>
+      <c r="F2">
+        <v>0.92</v>
+      </c>
       <c r="G2">
         <v>0.33</v>
       </c>
       <c r="H2" s="9">
         <v>0.77</v>
+      </c>
+      <c r="I2" s="9">
+        <v>0</v>
       </c>
       <c r="J2">
         <v>0.79</v>
@@ -1026,11 +1032,17 @@
       <c r="E3">
         <v>0.86</v>
       </c>
+      <c r="F3">
+        <v>0.95</v>
+      </c>
       <c r="G3">
         <v>0.64</v>
       </c>
       <c r="H3" s="9">
         <v>0.73</v>
+      </c>
+      <c r="I3" s="9">
+        <v>0.24</v>
       </c>
       <c r="J3">
         <v>0.25</v>
@@ -1053,11 +1065,17 @@
       <c r="E4">
         <v>0.86</v>
       </c>
+      <c r="F4">
+        <v>0.95</v>
+      </c>
       <c r="G4">
         <v>0.34</v>
       </c>
       <c r="H4" s="9">
         <v>0.56000000000000005</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0.03</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1080,11 +1098,17 @@
       <c r="E5">
         <v>0.86</v>
       </c>
+      <c r="F5">
+        <v>0.95</v>
+      </c>
       <c r="G5">
         <v>0.61</v>
       </c>
       <c r="H5" s="9">
-        <v>0.81</v>
+        <v>0.85</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0.34</v>
       </c>
       <c r="J5">
         <v>0.79</v>
@@ -1107,11 +1131,17 @@
       <c r="E6">
         <v>0.86</v>
       </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
       <c r="G6">
         <v>0.31</v>
       </c>
       <c r="H6" s="9">
         <v>0.63</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0.15</v>
       </c>
       <c r="J6">
         <v>0.77</v>
@@ -1134,11 +1164,17 @@
       <c r="E7">
         <v>0.79</v>
       </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
       <c r="G7">
         <v>0.37</v>
       </c>
       <c r="H7" s="9">
         <v>0.79</v>
+      </c>
+      <c r="I7" s="9">
+        <v>0.35</v>
       </c>
       <c r="J7">
         <v>0.79</v>
@@ -1161,11 +1197,17 @@
       <c r="E8">
         <v>0.93</v>
       </c>
+      <c r="F8">
+        <v>0.95</v>
+      </c>
       <c r="G8">
         <v>0.43</v>
       </c>
       <c r="H8" s="9">
         <v>0.83</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0.79</v>
@@ -1188,11 +1230,17 @@
       <c r="E9">
         <v>0.96</v>
       </c>
+      <c r="F9">
+        <v>0.92</v>
+      </c>
       <c r="G9">
         <v>0.49</v>
       </c>
       <c r="H9" s="9">
         <v>0.65</v>
+      </c>
+      <c r="I9" s="9">
+        <v>0.13</v>
       </c>
       <c r="J9">
         <v>0.25</v>
@@ -1215,11 +1263,17 @@
       <c r="E10">
         <v>0.86</v>
       </c>
+      <c r="F10">
+        <v>0.95</v>
+      </c>
       <c r="G10">
         <v>0.69</v>
       </c>
       <c r="H10" s="9">
         <v>0.75</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0.14000000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1242,11 +1296,17 @@
       <c r="E11">
         <v>0.93</v>
       </c>
+      <c r="F11">
+        <v>0.95</v>
+      </c>
       <c r="G11">
         <v>0.45</v>
       </c>
       <c r="H11" s="9">
         <v>0.85</v>
+      </c>
+      <c r="I11" s="9">
+        <v>0.18</v>
       </c>
       <c r="J11">
         <v>0.77</v>
@@ -1269,11 +1329,17 @@
       <c r="E12">
         <v>0.79</v>
       </c>
+      <c r="F12">
+        <v>0.93</v>
+      </c>
       <c r="G12">
         <v>0.22</v>
       </c>
       <c r="H12" s="9">
         <v>0.85</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0.27</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1296,11 +1362,17 @@
       <c r="E13">
         <v>0.96</v>
       </c>
+      <c r="F13">
+        <v>0.65</v>
+      </c>
       <c r="G13">
         <v>0.84</v>
       </c>
       <c r="H13" s="9">
         <v>0.96</v>
+      </c>
+      <c r="I13" s="9">
+        <v>0.53</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1323,11 +1395,17 @@
       <c r="E14">
         <v>0.93</v>
       </c>
+      <c r="F14">
+        <v>0.95</v>
+      </c>
       <c r="G14">
         <v>0.36</v>
       </c>
       <c r="H14" s="9">
         <v>0.9</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0.24</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -1350,11 +1428,17 @@
       <c r="E15">
         <v>0.86</v>
       </c>
+      <c r="F15">
+        <v>0.92</v>
+      </c>
       <c r="G15">
         <v>0.4</v>
       </c>
       <c r="H15" s="9">
         <v>1</v>
+      </c>
+      <c r="I15" s="9">
+        <v>0.31</v>
       </c>
       <c r="J15">
         <v>0.25</v>
@@ -1377,11 +1461,17 @@
       <c r="E16">
         <v>0.79</v>
       </c>
+      <c r="F16">
+        <v>0.82</v>
+      </c>
       <c r="G16">
         <v>0.33</v>
       </c>
       <c r="H16" s="9">
         <v>0.71</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0.08</v>
       </c>
       <c r="J16">
         <v>0.79</v>
@@ -1404,11 +1494,17 @@
       <c r="E17">
         <v>0.86</v>
       </c>
+      <c r="F17">
+        <v>0.95</v>
+      </c>
       <c r="G17">
         <v>0.49</v>
       </c>
       <c r="H17" s="9">
         <v>0.9</v>
+      </c>
+      <c r="I17" s="9">
+        <v>0.24</v>
       </c>
       <c r="J17">
         <v>0.25</v>
@@ -1431,11 +1527,17 @@
       <c r="E18">
         <v>0.89</v>
       </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
       <c r="G18">
         <v>0.34</v>
       </c>
       <c r="H18" s="9">
         <v>0.91</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0.16</v>
       </c>
       <c r="J18">
         <v>0.79</v>
@@ -1458,11 +1560,17 @@
       <c r="E19">
         <v>0.82</v>
       </c>
+      <c r="F19">
+        <v>0.88</v>
+      </c>
       <c r="G19">
         <v>0.56999999999999995</v>
       </c>
       <c r="H19" s="9">
         <v>0.73</v>
+      </c>
+      <c r="I19" s="9">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="J19">
         <v>0.79</v>
@@ -1485,11 +1593,17 @@
       <c r="E20">
         <v>0.86</v>
       </c>
+      <c r="F20">
+        <v>0.95</v>
+      </c>
       <c r="G20">
         <v>0.46</v>
       </c>
       <c r="H20" s="9">
         <v>0.79</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0.2</v>
       </c>
       <c r="J20">
         <v>0.79</v>
@@ -1512,11 +1626,17 @@
       <c r="E21">
         <v>0.89</v>
       </c>
+      <c r="F21">
+        <v>0.85</v>
+      </c>
       <c r="G21">
         <v>0.6</v>
       </c>
       <c r="H21" s="9">
         <v>0.9</v>
+      </c>
+      <c r="I21" s="9">
+        <v>0</v>
       </c>
       <c r="J21">
         <v>0.79</v>
@@ -1539,11 +1659,17 @@
       <c r="E22">
         <v>0.82</v>
       </c>
+      <c r="F22">
+        <v>0.95</v>
+      </c>
       <c r="G22">
         <v>0.43</v>
       </c>
       <c r="H22" s="9">
         <v>0.89</v>
+      </c>
+      <c r="I22" s="9">
+        <v>0.4</v>
       </c>
       <c r="J22">
         <v>0.79</v>
@@ -1566,11 +1692,17 @@
       <c r="E23">
         <v>0.93</v>
       </c>
+      <c r="F23">
+        <v>0.95</v>
+      </c>
       <c r="G23">
         <v>0.51</v>
       </c>
       <c r="H23" s="9">
         <v>0.88</v>
+      </c>
+      <c r="I23" s="9">
+        <v>0</v>
       </c>
       <c r="J23">
         <v>0.79</v>
@@ -1593,11 +1725,17 @@
       <c r="E24">
         <v>0.89</v>
       </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
       <c r="G24">
         <v>0.6</v>
       </c>
       <c r="H24" s="9">
         <v>0.71</v>
+      </c>
+      <c r="I24" s="9">
+        <v>0</v>
       </c>
       <c r="J24">
         <v>0.77</v>
@@ -1620,11 +1758,17 @@
       <c r="E25">
         <v>0.86</v>
       </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
       <c r="G25">
         <v>0.61</v>
       </c>
       <c r="H25" s="9">
         <v>0.88</v>
+      </c>
+      <c r="I25" s="9">
+        <v>0.1</v>
       </c>
       <c r="J25">
         <v>0.79</v>
@@ -1647,11 +1791,17 @@
       <c r="E26">
         <v>0.89</v>
       </c>
+      <c r="F26">
+        <v>0.72</v>
+      </c>
       <c r="G26">
         <v>0.33</v>
       </c>
       <c r="H26" s="9">
         <v>0.77</v>
+      </c>
+      <c r="I26" s="9">
+        <v>0</v>
       </c>
       <c r="J26">
         <v>0.79</v>
@@ -1674,11 +1824,17 @@
       <c r="E27">
         <v>0.93</v>
       </c>
+      <c r="F27">
+        <v>0.97</v>
+      </c>
       <c r="G27">
         <v>0.84</v>
       </c>
       <c r="H27" s="9">
         <v>0.65</v>
+      </c>
+      <c r="I27" s="9">
+        <v>0.27</v>
       </c>
       <c r="J27">
         <v>0.74</v>
@@ -1701,11 +1857,17 @@
       <c r="E28">
         <v>0.96</v>
       </c>
+      <c r="F28">
+        <v>0.95</v>
+      </c>
       <c r="G28">
         <v>0.6</v>
       </c>
       <c r="H28" s="9">
         <v>0.88</v>
+      </c>
+      <c r="I28" s="9">
+        <v>0.39</v>
       </c>
       <c r="J28">
         <v>0.79</v>
@@ -1728,11 +1890,17 @@
       <c r="E29">
         <v>0.89</v>
       </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
       <c r="G29">
         <v>0.46</v>
       </c>
       <c r="H29" s="9">
         <v>0.56000000000000005</v>
+      </c>
+      <c r="I29" s="9">
+        <v>0</v>
       </c>
       <c r="J29">
         <v>0.79</v>
@@ -1755,11 +1923,17 @@
       <c r="E30">
         <v>0.79</v>
       </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
       <c r="G30">
         <v>0.69</v>
       </c>
       <c r="H30" s="9">
         <v>0.88</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0</v>
       </c>
       <c r="J30">
         <v>0.77</v>
@@ -1782,11 +1956,17 @@
       <c r="E31">
         <v>0.89</v>
       </c>
+      <c r="F31">
+        <v>0.95</v>
+      </c>
       <c r="G31">
         <v>0.84</v>
       </c>
       <c r="H31" s="9">
         <v>0.88</v>
+      </c>
+      <c r="I31" s="9">
+        <v>0.56000000000000005</v>
       </c>
       <c r="J31">
         <v>0.74</v>
@@ -1809,11 +1989,17 @@
       <c r="E32">
         <v>0</v>
       </c>
+      <c r="F32">
+        <v>0.73</v>
+      </c>
       <c r="G32">
         <v>0.45</v>
       </c>
       <c r="H32" s="9">
         <v>0.67</v>
+      </c>
+      <c r="I32" s="9">
+        <v>0</v>
       </c>
       <c r="J32">
         <v>0.77</v>
@@ -1836,11 +2022,17 @@
       <c r="E33">
         <v>0.79</v>
       </c>
+      <c r="F33">
+        <v>0.95</v>
+      </c>
       <c r="G33">
         <v>0.66</v>
       </c>
       <c r="H33" s="9">
         <v>0.56000000000000005</v>
+      </c>
+      <c r="I33" s="9">
+        <v>0</v>
       </c>
       <c r="J33">
         <v>0.71</v>
@@ -1863,11 +2055,17 @@
       <c r="E34">
         <v>0.89</v>
       </c>
+      <c r="F34">
+        <v>0.95</v>
+      </c>
       <c r="G34">
         <v>0.25</v>
       </c>
       <c r="H34" s="9">
         <v>0.79</v>
+      </c>
+      <c r="I34" s="9">
+        <v>0.28000000000000003</v>
       </c>
       <c r="J34">
         <v>0.74</v>
@@ -1890,11 +2088,17 @@
       <c r="E35">
         <v>1</v>
       </c>
+      <c r="F35">
+        <v>0.95</v>
+      </c>
       <c r="G35">
         <v>0.24</v>
       </c>
       <c r="H35" s="9">
         <v>0.77</v>
+      </c>
+      <c r="I35" s="9">
+        <v>0.26</v>
       </c>
       <c r="J35">
         <v>0.71</v>
@@ -1917,11 +2121,17 @@
       <c r="E36">
         <v>0.82</v>
       </c>
+      <c r="F36">
+        <v>0.95</v>
+      </c>
       <c r="G36">
         <v>0.42</v>
       </c>
       <c r="H36" s="9">
         <v>0.63</v>
+      </c>
+      <c r="I36" s="9">
+        <v>0</v>
       </c>
       <c r="J36">
         <v>0.79</v>
@@ -1944,11 +2154,17 @@
       <c r="E37">
         <v>0.79</v>
       </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
       <c r="G37">
         <v>0.61</v>
       </c>
       <c r="H37" s="9">
         <v>0.79</v>
+      </c>
+      <c r="I37" s="9">
+        <v>0.26</v>
       </c>
       <c r="J37">
         <v>0.77</v>
@@ -1971,11 +2187,17 @@
       <c r="E38">
         <v>0.71</v>
       </c>
+      <c r="F38">
+        <v>0.95</v>
+      </c>
       <c r="G38">
         <v>0.45</v>
       </c>
       <c r="H38" s="9">
         <v>0.71</v>
+      </c>
+      <c r="I38" s="9">
+        <v>0</v>
       </c>
       <c r="J38">
         <v>0.77</v>
@@ -1998,11 +2220,17 @@
       <c r="E39">
         <v>0.93</v>
       </c>
+      <c r="F39">
+        <v>0.95</v>
+      </c>
       <c r="G39">
         <v>0.56000000000000005</v>
       </c>
       <c r="H39" s="9">
         <v>0.77</v>
+      </c>
+      <c r="I39" s="9">
+        <v>0.26</v>
       </c>
       <c r="J39">
         <v>0.79</v>
@@ -2025,11 +2253,17 @@
       <c r="E40">
         <v>0.79</v>
       </c>
+      <c r="F40">
+        <v>0.95</v>
+      </c>
       <c r="G40">
         <v>0.22</v>
       </c>
       <c r="H40" s="9">
         <v>0.69</v>
+      </c>
+      <c r="I40" s="9">
+        <v>0.12</v>
       </c>
       <c r="J40">
         <v>0.77</v>
@@ -2052,11 +2286,17 @@
       <c r="E41">
         <v>1</v>
       </c>
+      <c r="F41">
+        <v>0.77</v>
+      </c>
       <c r="G41">
         <v>0.43</v>
       </c>
       <c r="H41" s="9">
         <v>0.63</v>
+      </c>
+      <c r="I41" s="9">
+        <v>0</v>
       </c>
       <c r="J41">
         <v>0.71</v>
@@ -2079,11 +2319,17 @@
       <c r="E42">
         <v>0.96</v>
       </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
       <c r="G42">
         <v>0.6</v>
       </c>
       <c r="H42" s="9">
         <v>0.9</v>
+      </c>
+      <c r="I42" s="9">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="J42">
         <v>0.77</v>
@@ -2106,11 +2352,17 @@
       <c r="E43">
         <v>0.93</v>
       </c>
+      <c r="F43">
+        <v>0.9</v>
+      </c>
       <c r="G43">
         <v>0.63</v>
       </c>
       <c r="H43" s="9">
         <v>0.9</v>
+      </c>
+      <c r="I43" s="9">
+        <v>0</v>
       </c>
       <c r="J43">
         <v>0.71</v>
@@ -2133,11 +2385,17 @@
       <c r="E44">
         <v>0.89</v>
       </c>
+      <c r="F44">
+        <v>0.95</v>
+      </c>
       <c r="G44">
         <v>0.63</v>
       </c>
       <c r="H44" s="9">
         <v>0.85</v>
+      </c>
+      <c r="I44" s="9">
+        <v>0</v>
       </c>
       <c r="J44">
         <v>0.79</v>
@@ -2160,11 +2418,17 @@
       <c r="E45">
         <v>1</v>
       </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
       <c r="G45">
         <v>0.46</v>
       </c>
       <c r="H45" s="9">
         <v>0.79</v>
+      </c>
+      <c r="I45" s="9">
+        <v>0.11</v>
       </c>
       <c r="J45">
         <v>0.79</v>
@@ -2187,11 +2451,17 @@
       <c r="E46">
         <v>0.79</v>
       </c>
+      <c r="F46">
+        <v>0.88</v>
+      </c>
       <c r="G46">
         <v>0.61</v>
       </c>
       <c r="H46" s="9">
         <v>0.81</v>
+      </c>
+      <c r="I46" s="9">
+        <v>0</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -2214,11 +2484,17 @@
       <c r="E47">
         <v>0.89</v>
       </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
       <c r="G47">
         <v>0.45</v>
       </c>
       <c r="H47" s="9">
         <v>0.94</v>
+      </c>
+      <c r="I47" s="9">
+        <v>0.35</v>
       </c>
       <c r="J47">
         <v>0.74</v>
@@ -2241,11 +2517,17 @@
       <c r="E48">
         <v>0.89</v>
       </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
       <c r="G48">
         <v>0.49</v>
       </c>
       <c r="H48" s="9">
         <v>0.81</v>
+      </c>
+      <c r="I48" s="9">
+        <v>0</v>
       </c>
       <c r="J48">
         <v>0.73</v>
@@ -2268,11 +2550,17 @@
       <c r="E49">
         <v>0.86</v>
       </c>
+      <c r="F49">
+        <v>0.82</v>
+      </c>
       <c r="G49">
         <v>0.46</v>
       </c>
       <c r="H49" s="9">
         <v>0.65</v>
+      </c>
+      <c r="I49" s="9">
+        <v>0.2</v>
       </c>
       <c r="J49">
         <v>0.77</v>
@@ -2295,11 +2583,17 @@
       <c r="E50">
         <v>0.93</v>
       </c>
+      <c r="F50">
+        <v>0.88</v>
+      </c>
       <c r="G50">
         <v>0.43</v>
       </c>
       <c r="H50" s="9">
         <v>0.48</v>
+      </c>
+      <c r="I50" s="9">
+        <v>0</v>
       </c>
       <c r="J50">
         <v>0.73</v>
@@ -2322,11 +2616,17 @@
       <c r="E51">
         <v>0.89</v>
       </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
       <c r="G51">
         <v>0.34</v>
       </c>
       <c r="H51" s="9">
         <v>0.68</v>
+      </c>
+      <c r="I51" s="9">
+        <v>0.12</v>
       </c>
       <c r="J51">
         <v>0.74</v>
@@ -2349,11 +2649,17 @@
       <c r="E52">
         <v>0.79</v>
       </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
       <c r="G52">
         <v>0.61</v>
       </c>
       <c r="H52" s="9">
         <v>0.67</v>
+      </c>
+      <c r="I52" s="9">
+        <v>0</v>
       </c>
       <c r="J52">
         <v>0.74</v>
@@ -2376,11 +2682,17 @@
       <c r="E53">
         <v>0.89</v>
       </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
       <c r="G53">
         <v>0.51</v>
       </c>
       <c r="H53" s="9">
         <v>0.83</v>
+      </c>
+      <c r="I53" s="9">
+        <v>0.39</v>
       </c>
       <c r="J53">
         <v>0.77</v>
@@ -2403,11 +2715,17 @@
       <c r="E54">
         <v>0.89</v>
       </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
       <c r="G54">
         <v>0.49</v>
       </c>
       <c r="H54" s="9">
         <v>0.71</v>
+      </c>
+      <c r="I54" s="9">
+        <v>0</v>
       </c>
       <c r="J54">
         <v>0.73</v>
@@ -2430,11 +2748,17 @@
       <c r="E55">
         <v>0.79</v>
       </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
       <c r="G55">
         <v>0.45</v>
       </c>
       <c r="H55" s="9">
         <v>0.67</v>
+      </c>
+      <c r="I55" s="9">
+        <v>0</v>
       </c>
       <c r="J55">
         <v>0.74</v>
@@ -2457,11 +2781,17 @@
       <c r="E56">
         <v>0.96</v>
       </c>
+      <c r="F56">
+        <v>0.8</v>
+      </c>
       <c r="G56">
         <v>0.28000000000000003</v>
       </c>
       <c r="H56" s="9">
         <v>0.73</v>
+      </c>
+      <c r="I56" s="9">
+        <v>0.05</v>
       </c>
       <c r="J56">
         <v>0.73</v>
@@ -2484,11 +2814,17 @@
       <c r="E57">
         <v>0.64</v>
       </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
       <c r="G57">
         <v>0</v>
       </c>
       <c r="H57" s="9">
         <v>0.57999999999999996</v>
+      </c>
+      <c r="I57" s="9">
+        <v>0.13</v>
       </c>
       <c r="J57">
         <v>0.73</v>
@@ -2511,11 +2847,17 @@
       <c r="E58">
         <v>0.89</v>
       </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
       <c r="G58">
         <v>0.57999999999999996</v>
       </c>
       <c r="H58" s="9">
         <v>0.65</v>
+      </c>
+      <c r="I58" s="9">
+        <v>0</v>
       </c>
       <c r="J58">
         <v>0.73</v>
@@ -2538,11 +2880,17 @@
       <c r="E59">
         <v>0.79</v>
       </c>
+      <c r="F59">
+        <v>0.92</v>
+      </c>
       <c r="G59">
         <v>0.52</v>
       </c>
       <c r="H59" s="9">
         <v>0.69</v>
+      </c>
+      <c r="I59" s="9">
+        <v>0</v>
       </c>
       <c r="J59">
         <v>0.77</v>
@@ -2565,11 +2913,17 @@
       <c r="E60">
         <v>0.96</v>
       </c>
+      <c r="F60">
+        <v>0.82</v>
+      </c>
       <c r="G60">
         <v>0.43</v>
       </c>
       <c r="H60" s="9">
         <v>0.57999999999999996</v>
+      </c>
+      <c r="I60" s="9">
+        <v>0.03</v>
       </c>
       <c r="J60">
         <v>0.73</v>

--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80BC94C-E2D0-CD43-8CB0-D219096AEF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A76519-07FF-524A-9640-BDBAA9FEE5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="1040" windowWidth="26940" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -531,7 +531,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -549,6 +549,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1014,6 +1017,9 @@
       <c r="J2">
         <v>0.79</v>
       </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
       <c r="M2" s="7"/>
     </row>
     <row r="3" spans="1:13">
@@ -1047,6 +1053,9 @@
       <c r="J3">
         <v>0.25</v>
       </c>
+      <c r="L3">
+        <v>0.78</v>
+      </c>
       <c r="M3" s="7"/>
     </row>
     <row r="4" spans="1:13">
@@ -1080,6 +1089,9 @@
       <c r="J4">
         <v>0</v>
       </c>
+      <c r="L4">
+        <v>0.7</v>
+      </c>
       <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:13">
@@ -1113,6 +1125,9 @@
       <c r="J5">
         <v>0.79</v>
       </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
       <c r="M5" s="7"/>
     </row>
     <row r="6" spans="1:13">
@@ -1146,6 +1161,9 @@
       <c r="J6">
         <v>0.77</v>
       </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13">
@@ -1179,6 +1197,9 @@
       <c r="J7">
         <v>0.79</v>
       </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
       <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:13">
@@ -1212,6 +1233,9 @@
       <c r="J8">
         <v>0.79</v>
       </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
       <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13">
@@ -1245,6 +1269,9 @@
       <c r="J9">
         <v>0.25</v>
       </c>
+      <c r="L9">
+        <v>0.78</v>
+      </c>
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13">
@@ -1278,6 +1305,9 @@
       <c r="J10">
         <v>0</v>
       </c>
+      <c r="L10">
+        <v>0.7</v>
+      </c>
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13">
@@ -1311,6 +1341,9 @@
       <c r="J11">
         <v>0.77</v>
       </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:13">
@@ -1344,6 +1377,9 @@
       <c r="J12">
         <v>0</v>
       </c>
+      <c r="L12">
+        <v>0.7</v>
+      </c>
       <c r="M12" s="4"/>
     </row>
     <row r="13" spans="1:13">
@@ -1377,6 +1413,9 @@
       <c r="J13">
         <v>0</v>
       </c>
+      <c r="L13">
+        <v>0.7</v>
+      </c>
       <c r="M13" s="4"/>
     </row>
     <row r="14" spans="1:13">
@@ -1410,6 +1449,9 @@
       <c r="J14">
         <v>0</v>
       </c>
+      <c r="L14">
+        <v>0.7</v>
+      </c>
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="1:13">
@@ -1443,6 +1485,9 @@
       <c r="J15">
         <v>0.25</v>
       </c>
+      <c r="L15">
+        <v>0.78</v>
+      </c>
       <c r="M15" s="4"/>
     </row>
     <row r="16" spans="1:13">
@@ -1476,6 +1521,9 @@
       <c r="J16">
         <v>0.79</v>
       </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
       <c r="M16" s="4"/>
     </row>
     <row r="17" spans="1:13">
@@ -1509,6 +1557,9 @@
       <c r="J17">
         <v>0.25</v>
       </c>
+      <c r="L17">
+        <v>0.78</v>
+      </c>
       <c r="M17" s="4"/>
     </row>
     <row r="18" spans="1:13">
@@ -1542,6 +1593,9 @@
       <c r="J18">
         <v>0.79</v>
       </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
       <c r="M18" s="4"/>
     </row>
     <row r="19" spans="1:13">
@@ -1575,6 +1629,9 @@
       <c r="J19">
         <v>0.79</v>
       </c>
+      <c r="L19">
+        <v>0.67</v>
+      </c>
       <c r="M19" s="4"/>
     </row>
     <row r="20" spans="1:13">
@@ -1608,6 +1665,9 @@
       <c r="J20">
         <v>0.79</v>
       </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
       <c r="M20" s="4"/>
     </row>
     <row r="21" spans="1:13">
@@ -1641,6 +1701,9 @@
       <c r="J21">
         <v>0.79</v>
       </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
       <c r="M21" s="4"/>
     </row>
     <row r="22" spans="1:13">
@@ -1674,6 +1737,9 @@
       <c r="J22">
         <v>0.79</v>
       </c>
+      <c r="L22">
+        <v>0.67</v>
+      </c>
       <c r="M22" s="4"/>
     </row>
     <row r="23" spans="1:13">
@@ -1707,6 +1773,9 @@
       <c r="J23">
         <v>0.79</v>
       </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
       <c r="M23" s="4"/>
     </row>
     <row r="24" spans="1:13">
@@ -1740,6 +1809,9 @@
       <c r="J24">
         <v>0.77</v>
       </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
       <c r="M24" s="4"/>
     </row>
     <row r="25" spans="1:13">
@@ -1773,6 +1845,9 @@
       <c r="J25">
         <v>0.79</v>
       </c>
+      <c r="L25">
+        <v>0.67</v>
+      </c>
       <c r="M25" s="4"/>
     </row>
     <row r="26" spans="1:13">
@@ -1806,6 +1881,9 @@
       <c r="J26">
         <v>0.79</v>
       </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
       <c r="M26" s="8"/>
     </row>
     <row r="27" spans="1:13">
@@ -1839,7 +1917,16 @@
       <c r="J27">
         <v>0.74</v>
       </c>
-      <c r="M27" s="4"/>
+      <c r="K27">
+        <v>0.95</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" s="10">
+        <f>(((LARGE(D27:F27,1)+LARGE(D27:F27,2))*0.2/2+(LARGE(G27:I27,1)+LARGE(G27:I27,2))*0.5/2+(LARGE(J27:L27,1)+LARGE(J27:L27,2))*0.3/2))</f>
+        <v>0.81600000000000006</v>
+      </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="6" t="s">
@@ -1872,6 +1959,9 @@
       <c r="J28">
         <v>0.79</v>
       </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
       <c r="M28" s="4"/>
     </row>
     <row r="29" spans="1:13">
@@ -1905,6 +1995,9 @@
       <c r="J29">
         <v>0.79</v>
       </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
       <c r="M29" s="4"/>
     </row>
     <row r="30" spans="1:13">
@@ -1938,6 +2031,9 @@
       <c r="J30">
         <v>0.77</v>
       </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
       <c r="M30" s="4"/>
     </row>
     <row r="31" spans="1:13">
@@ -1971,7 +2067,16 @@
       <c r="J31">
         <v>0.74</v>
       </c>
-      <c r="M31" s="4"/>
+      <c r="K31">
+        <v>0.95</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" s="10">
+        <f>(((LARGE(D31:F31,1)+LARGE(D31:F31,2))*0.2/2+(LARGE(G31:I31,1)+LARGE(G31:I31,2))*0.5/2+(LARGE(J31:L31,1)+LARGE(J31:L31,2))*0.3/2))</f>
+        <v>0.86749999999999994</v>
+      </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="6" t="s">
@@ -2004,6 +2109,9 @@
       <c r="J32">
         <v>0.77</v>
       </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
       <c r="M32" s="8"/>
     </row>
     <row r="33" spans="1:13">
@@ -2037,6 +2145,9 @@
       <c r="J33">
         <v>0.71</v>
       </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
       <c r="M33" s="4"/>
     </row>
     <row r="34" spans="1:13">
@@ -2070,7 +2181,16 @@
       <c r="J34">
         <v>0.74</v>
       </c>
-      <c r="M34" s="4"/>
+      <c r="K34">
+        <v>0.95</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" s="10">
+        <f>(((LARGE(D34:F34,1)+LARGE(D34:F34,2))*0.2/2+(LARGE(G34:I34,1)+LARGE(G34:I34,2))*0.5/2+(LARGE(J34:L34,1)+LARGE(J34:L34,2))*0.3/2))</f>
+        <v>0.70500000000000007</v>
+      </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="6" t="s">
@@ -2103,6 +2223,9 @@
       <c r="J35">
         <v>0.71</v>
       </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
       <c r="M35" s="4"/>
     </row>
     <row r="36" spans="1:13">
@@ -2136,6 +2259,9 @@
       <c r="J36">
         <v>0.79</v>
       </c>
+      <c r="L36">
+        <v>0.67</v>
+      </c>
       <c r="M36" s="4"/>
     </row>
     <row r="37" spans="1:13">
@@ -2169,7 +2295,16 @@
       <c r="J37">
         <v>0.77</v>
       </c>
-      <c r="M37" s="4"/>
+      <c r="K37">
+        <v>0.85</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" s="10">
+        <f>(((LARGE(D37:F37,1)+LARGE(D37:F37,2))*0.2/2+(LARGE(G37:I37,1)+LARGE(G37:I37,2))*0.5/2+(LARGE(J37:L37,1)+LARGE(J37:L37,2))*0.3/2))</f>
+        <v>0.755</v>
+      </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="6" t="s">
@@ -2202,7 +2337,16 @@
       <c r="J38">
         <v>0.77</v>
       </c>
-      <c r="M38" s="4"/>
+      <c r="K38">
+        <v>0.85</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38" s="10">
+        <f>(((LARGE(D38:F38,1)+LARGE(D38:F38,2))*0.2/2+(LARGE(G38:I38,1)+LARGE(G38:I38,2))*0.5/2+(LARGE(J38:L38,1)+LARGE(J38:L38,2))*0.3/2))</f>
+        <v>0.71299999999999997</v>
+      </c>
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="6" t="s">
@@ -2235,6 +2379,9 @@
       <c r="J39">
         <v>0.79</v>
       </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
       <c r="M39" s="4"/>
     </row>
     <row r="40" spans="1:13">
@@ -2268,7 +2415,16 @@
       <c r="J40">
         <v>0.77</v>
       </c>
-      <c r="M40" s="4"/>
+      <c r="K40">
+        <v>0.85</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" s="10">
+        <f>(((LARGE(D40:F40,1)+LARGE(D40:F40,2))*0.2/2+(LARGE(G40:I40,1)+LARGE(G40:I40,2))*0.5/2+(LARGE(J40:L40,1)+LARGE(J40:L40,2))*0.3/2))</f>
+        <v>0.65149999999999997</v>
+      </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="6" t="s">
@@ -2301,6 +2457,9 @@
       <c r="J41">
         <v>0.71</v>
       </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
       <c r="M41" s="4"/>
     </row>
     <row r="42" spans="1:13">
@@ -2334,7 +2493,16 @@
       <c r="J42">
         <v>0.77</v>
       </c>
-      <c r="M42" s="8"/>
+      <c r="K42">
+        <v>0.85</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42" s="10">
+        <f>(((LARGE(D42:F42,1)+LARGE(D42:F42,2))*0.2/2+(LARGE(G42:I42,1)+LARGE(G42:I42,2))*0.5/2+(LARGE(J42:L42,1)+LARGE(J42:L42,2))*0.3/2))</f>
+        <v>0.79599999999999993</v>
+      </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="6" t="s">
@@ -2367,6 +2535,9 @@
       <c r="J43">
         <v>0.71</v>
       </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
       <c r="M43" s="8"/>
     </row>
     <row r="44" spans="1:13">
@@ -2400,6 +2571,9 @@
       <c r="J44">
         <v>0.79</v>
       </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
       <c r="M44" s="4"/>
     </row>
     <row r="45" spans="1:13">
@@ -2433,6 +2607,9 @@
       <c r="J45">
         <v>0.79</v>
       </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
       <c r="M45" s="4"/>
     </row>
     <row r="46" spans="1:13">
@@ -2466,6 +2643,9 @@
       <c r="J46">
         <v>0</v>
       </c>
+      <c r="L46">
+        <v>0.78</v>
+      </c>
       <c r="M46" s="4"/>
     </row>
     <row r="47" spans="1:13">
@@ -2499,7 +2679,16 @@
       <c r="J47">
         <v>0.74</v>
       </c>
-      <c r="M47" s="4"/>
+      <c r="K47">
+        <v>0.95</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" s="10">
+        <f>(((LARGE(D47:F47,1)+LARGE(D47:F47,2))*0.2/2+(LARGE(G47:I47,1)+LARGE(G47:I47,2))*0.5/2+(LARGE(J47:L47,1)+LARGE(J47:L47,2))*0.3/2))</f>
+        <v>0.76300000000000012</v>
+      </c>
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="6" t="s">
@@ -2532,6 +2721,9 @@
       <c r="J48">
         <v>0.73</v>
       </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
       <c r="M48" s="4"/>
     </row>
     <row r="49" spans="1:13">
@@ -2565,6 +2757,9 @@
       <c r="J49">
         <v>0.77</v>
       </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
       <c r="M49" s="4"/>
     </row>
     <row r="50" spans="1:13">
@@ -2598,6 +2793,9 @@
       <c r="J50">
         <v>0.73</v>
       </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
       <c r="M50" s="4"/>
     </row>
     <row r="51" spans="1:13">
@@ -2631,6 +2829,9 @@
       <c r="J51">
         <v>0.74</v>
       </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
       <c r="M51" s="4"/>
     </row>
     <row r="52" spans="1:13">
@@ -2664,6 +2865,9 @@
       <c r="J52">
         <v>0.74</v>
       </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
       <c r="M52" s="4"/>
     </row>
     <row r="53" spans="1:13">
@@ -2697,6 +2901,9 @@
       <c r="J53">
         <v>0.77</v>
       </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
       <c r="M53" s="4"/>
     </row>
     <row r="54" spans="1:13">
@@ -2730,6 +2937,9 @@
       <c r="J54">
         <v>0.73</v>
       </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
       <c r="M54" s="4"/>
     </row>
     <row r="55" spans="1:13">
@@ -2763,6 +2973,9 @@
       <c r="J55">
         <v>0.74</v>
       </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
       <c r="M55" s="4"/>
     </row>
     <row r="56" spans="1:13">
@@ -2796,6 +3009,9 @@
       <c r="J56">
         <v>0.73</v>
       </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
       <c r="M56" s="4"/>
     </row>
     <row r="57" spans="1:13">
@@ -2829,6 +3045,9 @@
       <c r="J57">
         <v>0.73</v>
       </c>
+      <c r="L57">
+        <v>0</v>
+      </c>
       <c r="M57" s="4"/>
     </row>
     <row r="58" spans="1:13">
@@ -2862,6 +3081,9 @@
       <c r="J58">
         <v>0.73</v>
       </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
       <c r="M58" s="4"/>
     </row>
     <row r="59" spans="1:13">
@@ -2895,6 +3117,9 @@
       <c r="J59">
         <v>0.77</v>
       </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
       <c r="M59" s="4"/>
     </row>
     <row r="60" spans="1:13">
@@ -2927,6 +3152,9 @@
       </c>
       <c r="J60">
         <v>0.73</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
       </c>
       <c r="M60" s="4"/>
     </row>

--- a/cw11032026.xlsx
+++ b/cw11032026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A76519-07FF-524A-9640-BDBAA9FEE5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C5882A-51FA-F947-9DF7-D6B4944F3247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="1040" windowWidth="26940" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -531,7 +531,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -541,17 +541,20 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -560,6 +563,7 @@
   <dxfs count="3">
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -605,11 +609,11 @@
     <tableColumn id="1" xr3:uid="{1B9A59CC-67BA-3D4E-8BF2-E846FAA4CCF7}" name="Surname"/>
     <tableColumn id="2" xr3:uid="{F58DECFD-039A-A04B-8F5C-EAB87EBDF67E}" name="Reg" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{B367B5B8-26A8-004D-8405-A55D6B3FB2B6}" name="Dept"/>
-    <tableColumn id="4" xr3:uid="{248CFFC4-D566-4C47-A784-2D182108B777}" name="Quiz_1" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{248CFFC4-D566-4C47-A784-2D182108B777}" name="Quiz_1" dataDxfId="0"/>
     <tableColumn id="5" xr3:uid="{4A2A2B68-EF30-7742-9921-AE9C8CB19994}" name="Quiz_2"/>
     <tableColumn id="6" xr3:uid="{F4845CBF-1A2D-6F4D-8189-BDA9FF51FC40}" name="Quiz_3"/>
     <tableColumn id="7" xr3:uid="{C50393AC-DA9E-B244-B444-966939E941DB}" name="Test_1"/>
-    <tableColumn id="8" xr3:uid="{8357C7A6-F90C-A948-931D-7D4829EE9A20}" name="Test_2 " dataDxfId="0"/>
+    <tableColumn id="8" xr3:uid="{8357C7A6-F90C-A948-931D-7D4829EE9A20}" name="Test_2 " dataDxfId="1"/>
     <tableColumn id="9" xr3:uid="{AF37A560-C5F8-4E49-A224-CE84A49E046A}" name="Test_3 "/>
     <tableColumn id="10" xr3:uid="{E7DCE493-9761-F446-9017-EFE5CA173E6F}" name="AS_1"/>
     <tableColumn id="11" xr3:uid="{22CC7E9A-51CA-274B-9C92-B1E8F88F4324}" name="AS_2 "/>
@@ -940,8 +944,10 @@
   <dimension ref="A1:M228"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="6.140625" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" style="9" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" style="2"/>
   </cols>
   <sheetData>
@@ -955,7 +961,7 @@
       <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="9" t="s">
         <v>5</v>
       </c>
       <c r="E1" t="s">
@@ -996,7 +1002,7 @@
       <c r="C2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="10">
         <v>0.89</v>
       </c>
       <c r="E2">
@@ -1008,19 +1014,25 @@
       <c r="G2">
         <v>0.33</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="7">
         <v>0.77</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="7">
         <v>0</v>
       </c>
       <c r="J2">
         <v>0.79</v>
       </c>
+      <c r="K2">
+        <v>0.9</v>
+      </c>
       <c r="L2">
         <v>0</v>
       </c>
-      <c r="M2" s="7"/>
+      <c r="M2" s="8">
+        <f t="shared" ref="M2:M26" si="0">(((LARGE(D2:F2,1)+LARGE(D2:F2,2))*0.2/2+(LARGE(G2:I2,1)+LARGE(G2:I2,2))*0.5/2+(LARGE(J2:L2,1)+LARGE(J2:L2,2))*0.3/2))</f>
+        <v>0.72050000000000003</v>
+      </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="6" t="s">
@@ -1032,7 +1044,7 @@
       <c r="C3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="10">
         <v>0.92</v>
       </c>
       <c r="E3">
@@ -1044,19 +1056,25 @@
       <c r="G3">
         <v>0.64</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="7">
         <v>0.73</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="7">
         <v>0.24</v>
       </c>
       <c r="J3">
         <v>0.25</v>
       </c>
+      <c r="K3">
+        <v>0.8</v>
+      </c>
       <c r="L3">
         <v>0.78</v>
       </c>
-      <c r="M3" s="7"/>
+      <c r="M3" s="8">
+        <f t="shared" si="0"/>
+        <v>0.76650000000000007</v>
+      </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="6" t="s">
@@ -1068,7 +1086,7 @@
       <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="10">
         <v>0.85</v>
       </c>
       <c r="E4">
@@ -1080,19 +1098,25 @@
       <c r="G4">
         <v>0.34</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="7">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="7">
         <v>0.03</v>
       </c>
       <c r="J4">
         <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0.88</v>
       </c>
       <c r="L4">
         <v>0.7</v>
       </c>
-      <c r="M4" s="7"/>
+      <c r="M4" s="8">
+        <f t="shared" si="0"/>
+        <v>0.64300000000000002</v>
+      </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="6" t="s">
@@ -1104,7 +1128,7 @@
       <c r="C5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="10">
         <v>0.82</v>
       </c>
       <c r="E5">
@@ -1116,19 +1140,25 @@
       <c r="G5">
         <v>0.61</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="7">
         <v>0.85</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="7">
         <v>0.34</v>
       </c>
       <c r="J5">
         <v>0.79</v>
       </c>
+      <c r="K5">
+        <v>0.88</v>
+      </c>
       <c r="L5">
         <v>0</v>
       </c>
-      <c r="M5" s="7"/>
+      <c r="M5" s="8">
+        <f t="shared" si="0"/>
+        <v>0.79649999999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="6" t="s">
@@ -1140,7 +1170,7 @@
       <c r="C6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="10">
         <v>0.8</v>
       </c>
       <c r="E6">
@@ -1152,19 +1182,25 @@
       <c r="G6">
         <v>0.31</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="7">
         <v>0.63</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="7">
         <v>0.15</v>
       </c>
       <c r="J6">
         <v>0.77</v>
       </c>
+      <c r="K6">
+        <v>0.9</v>
+      </c>
       <c r="L6">
         <v>0</v>
       </c>
-      <c r="M6" s="4"/>
+      <c r="M6" s="8">
+        <f t="shared" si="0"/>
+        <v>0.65149999999999997</v>
+      </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="6" t="s">
@@ -1176,7 +1212,7 @@
       <c r="C7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="10">
         <v>0.86</v>
       </c>
       <c r="E7">
@@ -1188,19 +1224,25 @@
       <c r="G7">
         <v>0.37</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="7">
         <v>0.79</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="7">
         <v>0.35</v>
       </c>
       <c r="J7">
         <v>0.79</v>
       </c>
+      <c r="K7">
+        <v>0.9</v>
+      </c>
       <c r="L7">
         <v>0</v>
       </c>
-      <c r="M7" s="4"/>
+      <c r="M7" s="8">
+        <f t="shared" si="0"/>
+        <v>0.70850000000000013</v>
+      </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="6" t="s">
@@ -1212,7 +1254,7 @@
       <c r="C8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="10">
         <v>0.92</v>
       </c>
       <c r="E8">
@@ -1224,19 +1266,25 @@
       <c r="G8">
         <v>0.43</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="7">
         <v>0.83</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="7">
         <v>0</v>
       </c>
       <c r="J8">
         <v>0.79</v>
       </c>
+      <c r="K8">
+        <v>0.88</v>
+      </c>
       <c r="L8">
         <v>0</v>
       </c>
-      <c r="M8" s="4"/>
+      <c r="M8" s="8">
+        <f t="shared" si="0"/>
+        <v>0.75350000000000006</v>
+      </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
@@ -1248,7 +1296,7 @@
       <c r="C9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="10">
         <v>0.97</v>
       </c>
       <c r="E9">
@@ -1260,19 +1308,25 @@
       <c r="G9">
         <v>0.49</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="7">
         <v>0.65</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="7">
         <v>0.13</v>
       </c>
       <c r="J9">
         <v>0.25</v>
       </c>
+      <c r="K9">
+        <v>0.8</v>
+      </c>
       <c r="L9">
         <v>0.78</v>
       </c>
-      <c r="M9" s="4"/>
+      <c r="M9" s="8">
+        <f t="shared" si="0"/>
+        <v>0.71500000000000008</v>
+      </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="6" t="s">
@@ -1284,7 +1338,7 @@
       <c r="C10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="10">
         <v>0.7</v>
       </c>
       <c r="E10">
@@ -1296,19 +1350,25 @@
       <c r="G10">
         <v>0.69</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="7">
         <v>0.75</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="7">
         <v>0.14000000000000001</v>
       </c>
       <c r="J10">
         <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.88</v>
       </c>
       <c r="L10">
         <v>0.7</v>
       </c>
-      <c r="M10" s="4"/>
+      <c r="M10" s="8">
+        <f t="shared" si="0"/>
+        <v>0.77800000000000002</v>
+      </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="6" t="s">
@@ -1320,7 +1380,7 @@
       <c r="C11" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="10">
         <v>0.86</v>
       </c>
       <c r="E11">
@@ -1332,19 +1392,25 @@
       <c r="G11">
         <v>0.45</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="7">
         <v>0.85</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="7">
         <v>0.18</v>
       </c>
       <c r="J11">
         <v>0.77</v>
       </c>
+      <c r="K11">
+        <v>0.9</v>
+      </c>
       <c r="L11">
         <v>0</v>
       </c>
-      <c r="M11" s="4"/>
+      <c r="M11" s="8">
+        <f t="shared" si="0"/>
+        <v>0.76350000000000007</v>
+      </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="6" t="s">
@@ -1356,7 +1422,7 @@
       <c r="C12" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="10">
         <v>0.86</v>
       </c>
       <c r="E12">
@@ -1368,19 +1434,25 @@
       <c r="G12">
         <v>0.22</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="7">
         <v>0.85</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="7">
         <v>0.27</v>
       </c>
       <c r="J12">
         <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0.88</v>
       </c>
       <c r="L12">
         <v>0.7</v>
       </c>
-      <c r="M12" s="4"/>
+      <c r="M12" s="8">
+        <f t="shared" si="0"/>
+        <v>0.69600000000000006</v>
+      </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="6" t="s">
@@ -1392,7 +1464,7 @@
       <c r="C13" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="10">
         <v>0.7</v>
       </c>
       <c r="E13">
@@ -1404,19 +1476,25 @@
       <c r="G13">
         <v>0.84</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="7">
         <v>0.96</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="7">
         <v>0.53</v>
       </c>
       <c r="J13">
         <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0.88</v>
       </c>
       <c r="L13">
         <v>0.7</v>
       </c>
-      <c r="M13" s="4"/>
+      <c r="M13" s="8">
+        <f t="shared" si="0"/>
+        <v>0.85299999999999998</v>
+      </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="6" t="s">
@@ -1428,7 +1506,7 @@
       <c r="C14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="10">
         <v>0.75</v>
       </c>
       <c r="E14">
@@ -1440,19 +1518,25 @@
       <c r="G14">
         <v>0.36</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="7">
         <v>0.9</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="7">
         <v>0.24</v>
       </c>
       <c r="J14">
         <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0.88</v>
       </c>
       <c r="L14">
         <v>0.7</v>
       </c>
-      <c r="M14" s="4"/>
+      <c r="M14" s="8">
+        <f t="shared" si="0"/>
+        <v>0.74</v>
+      </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="6" t="s">
@@ -1464,7 +1548,7 @@
       <c r="C15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="10">
         <v>0.92</v>
       </c>
       <c r="E15">
@@ -1476,19 +1560,25 @@
       <c r="G15">
         <v>0.4</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="7">
         <v>1</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="7">
         <v>0.31</v>
       </c>
       <c r="J15">
         <v>0.25</v>
       </c>
+      <c r="K15">
+        <v>0.8</v>
+      </c>
       <c r="L15">
         <v>0.78</v>
       </c>
-      <c r="M15" s="4"/>
+      <c r="M15" s="8">
+        <f t="shared" si="0"/>
+        <v>0.77100000000000002</v>
+      </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="6" t="s">
@@ -1500,7 +1590,7 @@
       <c r="C16" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="10">
         <v>0.76</v>
       </c>
       <c r="E16">
@@ -1512,19 +1602,25 @@
       <c r="G16">
         <v>0.33</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="7">
         <v>0.71</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="7">
         <v>0.08</v>
       </c>
       <c r="J16">
         <v>0.79</v>
       </c>
+      <c r="K16">
+        <v>0.9</v>
+      </c>
       <c r="L16">
         <v>0</v>
       </c>
-      <c r="M16" s="4"/>
+      <c r="M16" s="8">
+        <f t="shared" si="0"/>
+        <v>0.6745000000000001</v>
+      </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="6" t="s">
@@ -1536,7 +1632,7 @@
       <c r="C17" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="10">
         <v>0.87</v>
       </c>
       <c r="E17">
@@ -1548,19 +1644,25 @@
       <c r="G17">
         <v>0.49</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="7">
         <v>0.9</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="7">
         <v>0.24</v>
       </c>
       <c r="J17">
         <v>0.25</v>
       </c>
+      <c r="K17">
+        <v>0.8</v>
+      </c>
       <c r="L17">
         <v>0.78</v>
       </c>
-      <c r="M17" s="4"/>
+      <c r="M17" s="8">
+        <f t="shared" si="0"/>
+        <v>0.76650000000000007</v>
+      </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="6" t="s">
@@ -1572,7 +1674,7 @@
       <c r="C18" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="10">
         <v>0.94</v>
       </c>
       <c r="E18">
@@ -1584,19 +1686,25 @@
       <c r="G18">
         <v>0.34</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="7">
         <v>0.91</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="7">
         <v>0.16</v>
       </c>
       <c r="J18">
         <v>0.79</v>
       </c>
+      <c r="K18">
+        <v>0.88</v>
+      </c>
       <c r="L18">
         <v>0</v>
       </c>
-      <c r="M18" s="4"/>
+      <c r="M18" s="8">
+        <f t="shared" si="0"/>
+        <v>0.746</v>
+      </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="6" t="s">
@@ -1608,7 +1716,7 @@
       <c r="C19" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="10">
         <v>0.93</v>
       </c>
       <c r="E19">
@@ -1620,19 +1728,25 @@
       <c r="G19">
         <v>0.56999999999999995</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="7">
         <v>0.73</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="J19">
         <v>0.79</v>
       </c>
+      <c r="K19">
+        <v>0.9</v>
+      </c>
       <c r="L19">
         <v>0.67</v>
       </c>
-      <c r="M19" s="4"/>
+      <c r="M19" s="8">
+        <f t="shared" si="0"/>
+        <v>0.75950000000000006</v>
+      </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="6" t="s">
@@ -1644,7 +1758,7 @@
       <c r="C20" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="10">
         <v>0.7</v>
       </c>
       <c r="E20">
@@ -1656,19 +1770,25 @@
       <c r="G20">
         <v>0.46</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="7">
         <v>0.79</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="7">
         <v>0.2</v>
       </c>
       <c r="J20">
         <v>0.79</v>
       </c>
+      <c r="K20">
+        <v>0.9</v>
+      </c>
       <c r="L20">
         <v>0</v>
       </c>
-      <c r="M20" s="4"/>
+      <c r="M20" s="8">
+        <f t="shared" si="0"/>
+        <v>0.74700000000000011</v>
+      </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="6" t="s">
@@ -1680,7 +1800,7 @@
       <c r="C21" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="10">
         <v>0.85</v>
       </c>
       <c r="E21">
@@ -1692,19 +1812,25 @@
       <c r="G21">
         <v>0.6</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="7">
         <v>0.9</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="7">
         <v>0</v>
       </c>
       <c r="J21">
         <v>0.79</v>
       </c>
+      <c r="K21">
+        <v>0.88</v>
+      </c>
       <c r="L21">
         <v>0</v>
       </c>
-      <c r="M21" s="4"/>
+      <c r="M21" s="8">
+        <f t="shared" si="0"/>
+        <v>0.7995000000000001</v>
+      </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="6" t="s">
@@ -1716,7 +1842,7 @@
       <c r="C22" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="10">
         <v>0.73</v>
       </c>
       <c r="E22">
@@ -1728,19 +1854,25 @@
       <c r="G22">
         <v>0.43</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="7">
         <v>0.89</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="7">
         <v>0.4</v>
       </c>
       <c r="J22">
         <v>0.79</v>
       </c>
+      <c r="K22">
+        <v>0.9</v>
+      </c>
       <c r="L22">
         <v>0.67</v>
       </c>
-      <c r="M22" s="4"/>
+      <c r="M22" s="8">
+        <f t="shared" si="0"/>
+        <v>0.76049999999999995</v>
+      </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="6" t="s">
@@ -1752,7 +1884,7 @@
       <c r="C23" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="10">
         <v>0.8</v>
       </c>
       <c r="E23">
@@ -1764,19 +1896,25 @@
       <c r="G23">
         <v>0.51</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="7">
         <v>0.88</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="7">
         <v>0</v>
       </c>
       <c r="J23">
         <v>0.79</v>
       </c>
+      <c r="K23">
+        <v>0.88</v>
+      </c>
       <c r="L23">
         <v>0</v>
       </c>
-      <c r="M23" s="4"/>
+      <c r="M23" s="8">
+        <f t="shared" si="0"/>
+        <v>0.78600000000000003</v>
+      </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="6" t="s">
@@ -1788,7 +1926,7 @@
       <c r="C24" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="10">
         <v>0.9</v>
       </c>
       <c r="E24">
@@ -1800,19 +1938,25 @@
       <c r="G24">
         <v>0.6</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="7">
         <v>0.71</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="7">
         <v>0</v>
       </c>
       <c r="J24">
         <v>0.77</v>
       </c>
+      <c r="K24">
+        <v>0.9</v>
+      </c>
       <c r="L24">
         <v>0</v>
       </c>
-      <c r="M24" s="4"/>
+      <c r="M24" s="8">
+        <f t="shared" si="0"/>
+        <v>0.75700000000000012</v>
+      </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="6" t="s">
@@ -1824,7 +1968,7 @@
       <c r="C25" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="10">
         <v>0.83</v>
       </c>
       <c r="E25">
@@ -1836,19 +1980,25 @@
       <c r="G25">
         <v>0.61</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="7">
         <v>0.88</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="7">
         <v>0.1</v>
       </c>
       <c r="J25">
         <v>0.79</v>
       </c>
+      <c r="K25">
+        <v>0.9</v>
+      </c>
       <c r="L25">
         <v>0.67</v>
       </c>
-      <c r="M25" s="4"/>
+      <c r="M25" s="8">
+        <f t="shared" si="0"/>
+        <v>0.79499999999999993</v>
+      </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="6" t="s">
@@ -1860,7 +2010,7 @@
       <c r="C26" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="10">
         <v>0.63</v>
       </c>
       <c r="E26">
@@ -1872,19 +2022,25 @@
       <c r="G26">
         <v>0.33</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="7">
         <v>0.77</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="7">
         <v>0</v>
       </c>
       <c r="J26">
         <v>0.79</v>
       </c>
+      <c r="K26">
+        <v>0.88</v>
+      </c>
       <c r="L26">
         <v>0</v>
       </c>
-      <c r="M26" s="8"/>
+      <c r="M26" s="8">
+        <f t="shared" si="0"/>
+        <v>0.68650000000000011</v>
+      </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="6" t="s">
@@ -1896,7 +2052,7 @@
       <c r="C27" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="10">
         <v>0.9</v>
       </c>
       <c r="E27">
@@ -1908,10 +2064,10 @@
       <c r="G27">
         <v>0.84</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="7">
         <v>0.65</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="7">
         <v>0.27</v>
       </c>
       <c r="J27">
@@ -1923,7 +2079,7 @@
       <c r="L27">
         <v>0</v>
       </c>
-      <c r="M27" s="10">
+      <c r="M27" s="8">
         <f>(((LARGE(D27:F27,1)+LARGE(D27:F27,2))*0.2/2+(LARGE(G27:I27,1)+LARGE(G27:I27,2))*0.5/2+(LARGE(J27:L27,1)+LARGE(J27:L27,2))*0.3/2))</f>
         <v>0.81600000000000006</v>
       </c>
@@ -1938,7 +2094,7 @@
       <c r="C28" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="10">
         <v>0.94</v>
       </c>
       <c r="E28">
@@ -1950,19 +2106,25 @@
       <c r="G28">
         <v>0.6</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="7">
         <v>0.88</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="7">
         <v>0.39</v>
       </c>
       <c r="J28">
         <v>0.79</v>
       </c>
+      <c r="K28">
+        <v>0.88</v>
+      </c>
       <c r="L28">
         <v>0</v>
       </c>
-      <c r="M28" s="4"/>
+      <c r="M28" s="8">
+        <f t="shared" ref="M28:M60" si="1">(((LARGE(D28:F28,1)+LARGE(D28:F28,2))*0.2/2+(LARGE(G28:I28,1)+LARGE(G28:I28,2))*0.5/2+(LARGE(J28:L28,1)+LARGE(J28:L28,2))*0.3/2))</f>
+        <v>0.81149999999999989</v>
+      </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="6" t="s">
@@ -1974,7 +2136,7 @@
       <c r="C29" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="10">
         <v>0.93</v>
       </c>
       <c r="E29">
@@ -1986,19 +2148,25 @@
       <c r="G29">
         <v>0.46</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="7">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="7">
         <v>0</v>
       </c>
       <c r="J29">
         <v>0.79</v>
       </c>
+      <c r="K29">
+        <v>0.88</v>
+      </c>
       <c r="L29">
         <v>0</v>
       </c>
-      <c r="M29" s="4"/>
+      <c r="M29" s="8">
+        <f t="shared" si="1"/>
+        <v>0.6875</v>
+      </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="6" t="s">
@@ -2010,7 +2178,7 @@
       <c r="C30" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="10">
         <v>0.86</v>
       </c>
       <c r="E30">
@@ -2022,19 +2190,25 @@
       <c r="G30">
         <v>0.69</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="7">
         <v>0.88</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="7">
         <v>0</v>
       </c>
       <c r="J30">
         <v>0.77</v>
       </c>
+      <c r="K30">
+        <v>0.9</v>
+      </c>
       <c r="L30">
         <v>0</v>
       </c>
-      <c r="M30" s="4"/>
+      <c r="M30" s="8">
+        <f t="shared" si="1"/>
+        <v>0.80800000000000005</v>
+      </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="6" t="s">
@@ -2046,7 +2220,7 @@
       <c r="C31" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="10">
         <v>0.86</v>
       </c>
       <c r="E31">
@@ -2058,10 +2232,10 @@
       <c r="G31">
         <v>0.84</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="7">
         <v>0.88</v>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="7">
         <v>0.56000000000000005</v>
       </c>
       <c r="J31">
@@ -2073,8 +2247,8 @@
       <c r="L31">
         <v>0</v>
       </c>
-      <c r="M31" s="10">
-        <f>(((LARGE(D31:F31,1)+LARGE(D31:F31,2))*0.2/2+(LARGE(G31:I31,1)+LARGE(G31:I31,2))*0.5/2+(LARGE(J31:L31,1)+LARGE(J31:L31,2))*0.3/2))</f>
+      <c r="M31" s="8">
+        <f t="shared" si="1"/>
         <v>0.86749999999999994</v>
       </c>
     </row>
@@ -2088,7 +2262,7 @@
       <c r="C32" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="10">
         <v>0.82</v>
       </c>
       <c r="E32">
@@ -2100,19 +2274,25 @@
       <c r="G32">
         <v>0.45</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="7">
         <v>0.67</v>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="7">
         <v>0</v>
       </c>
       <c r="J32">
         <v>0.77</v>
       </c>
+      <c r="K32">
+        <v>0.9</v>
+      </c>
       <c r="L32">
         <v>0</v>
       </c>
-      <c r="M32" s="8"/>
+      <c r="M32" s="8">
+        <f t="shared" si="1"/>
+        <v>0.6855</v>
+      </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="6" t="s">
@@ -2124,7 +2304,7 @@
       <c r="C33" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="10">
         <v>0.96</v>
       </c>
       <c r="E33">
@@ -2136,19 +2316,25 @@
       <c r="G33">
         <v>0.66</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="7">
         <v>0.56000000000000005</v>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="7">
         <v>0</v>
       </c>
       <c r="J33">
         <v>0.71</v>
       </c>
+      <c r="K33">
+        <v>0.78</v>
+      </c>
       <c r="L33">
         <v>0</v>
       </c>
-      <c r="M33" s="4"/>
+      <c r="M33" s="8">
+        <f t="shared" si="1"/>
+        <v>0.71950000000000003</v>
+      </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="6" t="s">
@@ -2160,7 +2346,7 @@
       <c r="C34" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="10">
         <v>0.83</v>
       </c>
       <c r="E34">
@@ -2172,10 +2358,10 @@
       <c r="G34">
         <v>0.25</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="7">
         <v>0.79</v>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="7">
         <v>0.28000000000000003</v>
       </c>
       <c r="J34">
@@ -2187,8 +2373,8 @@
       <c r="L34">
         <v>0</v>
       </c>
-      <c r="M34" s="10">
-        <f>(((LARGE(D34:F34,1)+LARGE(D34:F34,2))*0.2/2+(LARGE(G34:I34,1)+LARGE(G34:I34,2))*0.5/2+(LARGE(J34:L34,1)+LARGE(J34:L34,2))*0.3/2))</f>
+      <c r="M34" s="8">
+        <f t="shared" si="1"/>
         <v>0.70500000000000007</v>
       </c>
     </row>
@@ -2202,7 +2388,7 @@
       <c r="C35" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="10">
         <v>0.89</v>
       </c>
       <c r="E35">
@@ -2214,19 +2400,25 @@
       <c r="G35">
         <v>0.24</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="7">
         <v>0.77</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="7">
         <v>0.26</v>
       </c>
       <c r="J35">
         <v>0.71</v>
       </c>
+      <c r="K35">
+        <v>0.78</v>
+      </c>
       <c r="L35">
         <v>0</v>
       </c>
-      <c r="M35" s="4"/>
+      <c r="M35" s="8">
+        <f t="shared" si="1"/>
+        <v>0.67600000000000005</v>
+      </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="6" t="s">
@@ -2238,7 +2430,7 @@
       <c r="C36" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="10">
         <v>0.82</v>
       </c>
       <c r="E36">
@@ -2250,19 +2442,25 @@
       <c r="G36">
         <v>0.42</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="7">
         <v>0.63</v>
       </c>
-      <c r="I36" s="9">
+      <c r="I36" s="7">
         <v>0</v>
       </c>
       <c r="J36">
         <v>0.79</v>
       </c>
+      <c r="K36">
+        <v>0.9</v>
+      </c>
       <c r="L36">
         <v>0.67</v>
       </c>
-      <c r="M36" s="4"/>
+      <c r="M36" s="8">
+        <f t="shared" si="1"/>
+        <v>0.69300000000000006</v>
+      </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="6" t="s">
@@ -2274,7 +2472,7 @@
       <c r="C37" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="10">
         <v>0.83</v>
       </c>
       <c r="E37">
@@ -2286,10 +2484,10 @@
       <c r="G37">
         <v>0.61</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="7">
         <v>0.79</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="7">
         <v>0.26</v>
       </c>
       <c r="J37">
@@ -2301,8 +2499,8 @@
       <c r="L37">
         <v>0</v>
       </c>
-      <c r="M37" s="10">
-        <f>(((LARGE(D37:F37,1)+LARGE(D37:F37,2))*0.2/2+(LARGE(G37:I37,1)+LARGE(G37:I37,2))*0.5/2+(LARGE(J37:L37,1)+LARGE(J37:L37,2))*0.3/2))</f>
+      <c r="M37" s="8">
+        <f t="shared" si="1"/>
         <v>0.755</v>
       </c>
     </row>
@@ -2316,7 +2514,7 @@
       <c r="C38" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="10">
         <v>0.85</v>
       </c>
       <c r="E38">
@@ -2328,10 +2526,10 @@
       <c r="G38">
         <v>0.45</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="7">
         <v>0.71</v>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="7">
         <v>0</v>
       </c>
       <c r="J38">
@@ -2343,8 +2541,8 @@
       <c r="L38">
         <v>0</v>
       </c>
-      <c r="M38" s="10">
-        <f>(((LARGE(D38:F38,1)+LARGE(D38:F38,2))*0.2/2+(LARGE(G38:I38,1)+LARGE(G38:I38,2))*0.5/2+(LARGE(J38:L38,1)+LARGE(J38:L38,2))*0.3/2))</f>
+      <c r="M38" s="8">
+        <f t="shared" si="1"/>
         <v>0.71299999999999997</v>
       </c>
     </row>
@@ -2358,7 +2556,7 @@
       <c r="C39" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="10">
         <v>0.89</v>
       </c>
       <c r="E39">
@@ -2370,19 +2568,25 @@
       <c r="G39">
         <v>0.56000000000000005</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="7">
         <v>0.77</v>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="7">
         <v>0.26</v>
       </c>
       <c r="J39">
         <v>0.79</v>
       </c>
+      <c r="K39">
+        <v>0.9</v>
+      </c>
       <c r="L39">
         <v>0</v>
       </c>
-      <c r="M39" s="4"/>
+      <c r="M39" s="8">
+        <f t="shared" si="1"/>
+        <v>0.77400000000000002</v>
+      </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="6" t="s">
@@ -2394,7 +2598,7 @@
       <c r="C40" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="10">
         <v>0.86</v>
       </c>
       <c r="E40">
@@ -2406,10 +2610,10 @@
       <c r="G40">
         <v>0.22</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="7">
         <v>0.69</v>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="7">
         <v>0.12</v>
       </c>
       <c r="J40">
@@ -2421,8 +2625,8 @@
       <c r="L40">
         <v>0</v>
       </c>
-      <c r="M40" s="10">
-        <f>(((LARGE(D40:F40,1)+LARGE(D40:F40,2))*0.2/2+(LARGE(G40:I40,1)+LARGE(G40:I40,2))*0.5/2+(LARGE(J40:L40,1)+LARGE(J40:L40,2))*0.3/2))</f>
+      <c r="M40" s="8">
+        <f t="shared" si="1"/>
         <v>0.65149999999999997</v>
       </c>
     </row>
@@ -2436,7 +2640,7 @@
       <c r="C41" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="10">
         <v>0.89</v>
       </c>
       <c r="E41">
@@ -2448,19 +2652,25 @@
       <c r="G41">
         <v>0.43</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="7">
         <v>0.63</v>
       </c>
-      <c r="I41" s="9">
+      <c r="I41" s="7">
         <v>0</v>
       </c>
       <c r="J41">
         <v>0.71</v>
       </c>
+      <c r="K41">
+        <v>0.78</v>
+      </c>
       <c r="L41">
         <v>0</v>
       </c>
-      <c r="M41" s="4"/>
+      <c r="M41" s="8">
+        <f t="shared" si="1"/>
+        <v>0.6775000000000001</v>
+      </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="6" t="s">
@@ -2472,7 +2682,7 @@
       <c r="C42" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="10">
         <v>0.82</v>
       </c>
       <c r="E42">
@@ -2484,10 +2694,10 @@
       <c r="G42">
         <v>0.6</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="7">
         <v>0.9</v>
       </c>
-      <c r="I42" s="9">
+      <c r="I42" s="7">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="J42">
@@ -2499,8 +2709,8 @@
       <c r="L42">
         <v>0</v>
       </c>
-      <c r="M42" s="10">
-        <f>(((LARGE(D42:F42,1)+LARGE(D42:F42,2))*0.2/2+(LARGE(G42:I42,1)+LARGE(G42:I42,2))*0.5/2+(LARGE(J42:L42,1)+LARGE(J42:L42,2))*0.3/2))</f>
+      <c r="M42" s="8">
+        <f t="shared" si="1"/>
         <v>0.79599999999999993</v>
       </c>
     </row>
@@ -2514,7 +2724,7 @@
       <c r="C43" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="10">
         <v>0.8</v>
       </c>
       <c r="E43">
@@ -2526,19 +2736,25 @@
       <c r="G43">
         <v>0.63</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="7">
         <v>0.9</v>
       </c>
-      <c r="I43" s="9">
+      <c r="I43" s="7">
         <v>0</v>
       </c>
       <c r="J43">
         <v>0.71</v>
       </c>
+      <c r="K43">
+        <v>0.78</v>
+      </c>
       <c r="L43">
         <v>0</v>
       </c>
-      <c r="M43" s="8"/>
+      <c r="M43" s="8">
+        <f t="shared" si="1"/>
+        <v>0.78900000000000003</v>
+      </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="6" t="s">
@@ -2550,7 +2766,7 @@
       <c r="C44" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="10">
         <v>0.85</v>
       </c>
       <c r="E44">
@@ -2562,19 +2778,25 @@
       <c r="G44">
         <v>0.63</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="7">
         <v>0.85</v>
       </c>
-      <c r="I44" s="9">
+      <c r="I44" s="7">
         <v>0</v>
       </c>
       <c r="J44">
         <v>0.79</v>
       </c>
+      <c r="K44">
+        <v>0.88</v>
+      </c>
       <c r="L44">
         <v>0</v>
       </c>
-      <c r="M44" s="4"/>
+      <c r="M44" s="8">
+        <f t="shared" si="1"/>
+        <v>0.80449999999999999</v>
+      </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="6" t="s">
@@ -2586,7 +2808,7 @@
       <c r="C45" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="10">
         <v>0.89</v>
       </c>
       <c r="E45">
@@ -2598,19 +2820,25 @@
       <c r="G45">
         <v>0.46</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="7">
         <v>0.79</v>
       </c>
-      <c r="I45" s="9">
+      <c r="I45" s="7">
         <v>0.11</v>
       </c>
       <c r="J45">
         <v>0.79</v>
       </c>
+      <c r="K45">
+        <v>0.88</v>
+      </c>
       <c r="L45">
         <v>0</v>
       </c>
-      <c r="M45" s="4"/>
+      <c r="M45" s="8">
+        <f t="shared" si="1"/>
+        <v>0.752</v>
+      </c>
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="6" t="s">
@@ -2622,7 +2850,7 @@
       <c r="C46" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="10">
         <v>0.97</v>
       </c>
       <c r="E46">
@@ -2634,19 +2862,25 @@
       <c r="G46">
         <v>0.61</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="7">
         <v>0.81</v>
       </c>
-      <c r="I46" s="9">
+      <c r="I46" s="7">
         <v>0</v>
       </c>
       <c r="J46">
         <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0.8</v>
       </c>
       <c r="L46">
         <v>0.78</v>
       </c>
-      <c r="M46" s="4"/>
+      <c r="M46" s="8">
+        <f t="shared" si="1"/>
+        <v>0.77700000000000002</v>
+      </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="6" t="s">
@@ -2658,7 +2892,7 @@
       <c r="C47" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="10">
         <v>0.73</v>
       </c>
       <c r="E47">
@@ -2670,10 +2904,10 @@
       <c r="G47">
         <v>0.45</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="7">
         <v>0.94</v>
       </c>
-      <c r="I47" s="9">
+      <c r="I47" s="7">
         <v>0.35</v>
       </c>
       <c r="J47">
@@ -2685,8 +2919,8 @@
       <c r="L47">
         <v>0</v>
       </c>
-      <c r="M47" s="10">
-        <f>(((LARGE(D47:F47,1)+LARGE(D47:F47,2))*0.2/2+(LARGE(G47:I47,1)+LARGE(G47:I47,2))*0.5/2+(LARGE(J47:L47,1)+LARGE(J47:L47,2))*0.3/2))</f>
+      <c r="M47" s="8">
+        <f t="shared" si="1"/>
         <v>0.76300000000000012</v>
       </c>
     </row>
@@ -2700,7 +2934,7 @@
       <c r="C48" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="10">
         <v>0.9</v>
       </c>
       <c r="E48">
@@ -2712,19 +2946,25 @@
       <c r="G48">
         <v>0.49</v>
       </c>
-      <c r="H48" s="9">
+      <c r="H48" s="7">
         <v>0.81</v>
       </c>
-      <c r="I48" s="9">
+      <c r="I48" s="7">
         <v>0</v>
       </c>
       <c r="J48">
         <v>0.73</v>
       </c>
+      <c r="K48">
+        <v>0.78</v>
+      </c>
       <c r="L48">
         <v>0</v>
       </c>
-      <c r="M48" s="4"/>
+      <c r="M48" s="8">
+        <f t="shared" si="1"/>
+        <v>0.73049999999999993</v>
+      </c>
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="6" t="s">
@@ -2736,7 +2976,7 @@
       <c r="C49" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="10">
         <v>0.83</v>
       </c>
       <c r="E49">
@@ -2748,19 +2988,25 @@
       <c r="G49">
         <v>0.46</v>
       </c>
-      <c r="H49" s="9">
+      <c r="H49" s="7">
         <v>0.65</v>
       </c>
-      <c r="I49" s="9">
+      <c r="I49" s="7">
         <v>0.2</v>
       </c>
       <c r="J49">
         <v>0.77</v>
       </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
       <c r="L49">
         <v>0</v>
       </c>
-      <c r="M49" s="4"/>
+      <c r="M49" s="8">
+        <f t="shared" si="1"/>
+        <v>0.56200000000000006</v>
+      </c>
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="6" t="s">
@@ -2772,7 +3018,7 @@
       <c r="C50" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="10">
         <v>0.85</v>
       </c>
       <c r="E50">
@@ -2784,19 +3030,25 @@
       <c r="G50">
         <v>0.43</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="7">
         <v>0.48</v>
       </c>
-      <c r="I50" s="9">
+      <c r="I50" s="7">
         <v>0</v>
       </c>
       <c r="J50">
         <v>0.73</v>
       </c>
+      <c r="K50">
+        <v>0.78</v>
+      </c>
       <c r="L50">
         <v>0</v>
       </c>
-      <c r="M50" s="4"/>
+      <c r="M50" s="8">
+        <f t="shared" si="1"/>
+        <v>0.63500000000000001</v>
+      </c>
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="6" t="s">
@@ -2808,7 +3060,7 @@
       <c r="C51" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="10">
         <v>0.7</v>
       </c>
       <c r="E51">
@@ -2820,19 +3072,25 @@
       <c r="G51">
         <v>0.34</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51" s="7">
         <v>0.68</v>
       </c>
-      <c r="I51" s="9">
+      <c r="I51" s="7">
         <v>0.12</v>
       </c>
       <c r="J51">
         <v>0.74</v>
       </c>
+      <c r="K51">
+        <v>0.9</v>
+      </c>
       <c r="L51">
         <v>0</v>
       </c>
-      <c r="M51" s="4"/>
+      <c r="M51" s="8">
+        <f t="shared" si="1"/>
+        <v>0.66</v>
+      </c>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="6" t="s">
@@ -2844,7 +3102,7 @@
       <c r="C52" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="10">
         <v>0.76</v>
       </c>
       <c r="E52">
@@ -2856,19 +3114,25 @@
       <c r="G52">
         <v>0.61</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52" s="7">
         <v>0.67</v>
       </c>
-      <c r="I52" s="9">
+      <c r="I52" s="7">
         <v>0</v>
       </c>
       <c r="J52">
         <v>0.74</v>
       </c>
+      <c r="K52">
+        <v>0.9</v>
+      </c>
       <c r="L52">
         <v>0</v>
       </c>
-      <c r="M52" s="4"/>
+      <c r="M52" s="8">
+        <f t="shared" si="1"/>
+        <v>0.72100000000000009</v>
+      </c>
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="6" t="s">
@@ -2880,7 +3144,7 @@
       <c r="C53" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="10">
         <v>0.9</v>
       </c>
       <c r="E53">
@@ -2892,19 +3156,25 @@
       <c r="G53">
         <v>0.51</v>
       </c>
-      <c r="H53" s="9">
+      <c r="H53" s="7">
         <v>0.83</v>
       </c>
-      <c r="I53" s="9">
+      <c r="I53" s="7">
         <v>0.39</v>
       </c>
       <c r="J53">
         <v>0.77</v>
       </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
       <c r="L53">
         <v>0</v>
       </c>
-      <c r="M53" s="4"/>
+      <c r="M53" s="8">
+        <f t="shared" si="1"/>
+        <v>0.62949999999999995</v>
+      </c>
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="6" t="s">
@@ -2916,7 +3186,7 @@
       <c r="C54" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54" s="10">
         <v>0.75</v>
       </c>
       <c r="E54">
@@ -2928,19 +3198,25 @@
       <c r="G54">
         <v>0.49</v>
       </c>
-      <c r="H54" s="9">
+      <c r="H54" s="7">
         <v>0.71</v>
       </c>
-      <c r="I54" s="9">
+      <c r="I54" s="7">
         <v>0</v>
       </c>
       <c r="J54">
         <v>0.73</v>
       </c>
+      <c r="K54">
+        <v>0.78</v>
+      </c>
       <c r="L54">
         <v>0</v>
       </c>
-      <c r="M54" s="4"/>
+      <c r="M54" s="8">
+        <f t="shared" si="1"/>
+        <v>0.6905</v>
+      </c>
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="6" t="s">
@@ -2952,7 +3228,7 @@
       <c r="C55" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="10">
         <v>0.69</v>
       </c>
       <c r="E55">
@@ -2964,19 +3240,25 @@
       <c r="G55">
         <v>0.45</v>
       </c>
-      <c r="H55" s="9">
+      <c r="H55" s="7">
         <v>0.67</v>
       </c>
-      <c r="I55" s="9">
+      <c r="I55" s="7">
         <v>0</v>
       </c>
       <c r="J55">
         <v>0.74</v>
       </c>
+      <c r="K55">
+        <v>0.9</v>
+      </c>
       <c r="L55">
         <v>0</v>
       </c>
-      <c r="M55" s="4"/>
+      <c r="M55" s="8">
+        <f t="shared" si="1"/>
+        <v>0.67400000000000004</v>
+      </c>
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="6" t="s">
@@ -2988,7 +3270,7 @@
       <c r="C56" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56" s="10">
         <v>0.18</v>
       </c>
       <c r="E56">
@@ -3000,19 +3282,25 @@
       <c r="G56">
         <v>0.28000000000000003</v>
       </c>
-      <c r="H56" s="9">
+      <c r="H56" s="7">
         <v>0.73</v>
       </c>
-      <c r="I56" s="9">
+      <c r="I56" s="7">
         <v>0.05</v>
       </c>
       <c r="J56">
         <v>0.73</v>
       </c>
+      <c r="K56">
+        <v>0.98</v>
+      </c>
       <c r="L56">
         <v>0</v>
       </c>
-      <c r="M56" s="4"/>
+      <c r="M56" s="8">
+        <f t="shared" si="1"/>
+        <v>0.68500000000000005</v>
+      </c>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="6" t="s">
@@ -3024,7 +3312,7 @@
       <c r="C57" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="10">
         <v>0.72</v>
       </c>
       <c r="E57">
@@ -3036,19 +3324,25 @@
       <c r="G57">
         <v>0</v>
       </c>
-      <c r="H57" s="9">
+      <c r="H57" s="7">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I57" s="9">
+      <c r="I57" s="7">
         <v>0.13</v>
       </c>
       <c r="J57">
         <v>0.73</v>
       </c>
+      <c r="K57">
+        <v>0.98</v>
+      </c>
       <c r="L57">
         <v>0</v>
       </c>
-      <c r="M57" s="4"/>
+      <c r="M57" s="8">
+        <f t="shared" si="1"/>
+        <v>0.57000000000000006</v>
+      </c>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="6" t="s">
@@ -3060,7 +3354,7 @@
       <c r="C58" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58" s="10">
         <v>0.77</v>
       </c>
       <c r="E58">
@@ -3072,19 +3366,25 @@
       <c r="G58">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H58" s="9">
+      <c r="H58" s="7">
         <v>0.65</v>
       </c>
-      <c r="I58" s="9">
+      <c r="I58" s="7">
         <v>0</v>
       </c>
       <c r="J58">
         <v>0.73</v>
       </c>
+      <c r="K58">
+        <v>0.98</v>
+      </c>
       <c r="L58">
         <v>0</v>
       </c>
-      <c r="M58" s="4"/>
+      <c r="M58" s="8">
+        <f t="shared" si="1"/>
+        <v>0.73</v>
+      </c>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="6" t="s">
@@ -3096,7 +3396,7 @@
       <c r="C59" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D59" s="10">
         <v>0.92</v>
       </c>
       <c r="E59">
@@ -3108,19 +3408,25 @@
       <c r="G59">
         <v>0.52</v>
       </c>
-      <c r="H59" s="9">
+      <c r="H59" s="7">
         <v>0.69</v>
       </c>
-      <c r="I59" s="9">
+      <c r="I59" s="7">
         <v>0</v>
       </c>
       <c r="J59">
         <v>0.77</v>
       </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
       <c r="L59">
         <v>0</v>
       </c>
-      <c r="M59" s="4"/>
+      <c r="M59" s="8">
+        <f t="shared" si="1"/>
+        <v>0.60200000000000009</v>
+      </c>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="6" t="s">
@@ -3132,7 +3438,7 @@
       <c r="C60" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D60" s="10">
         <v>0.66</v>
       </c>
       <c r="E60">
@@ -3144,32 +3450,38 @@
       <c r="G60">
         <v>0.43</v>
       </c>
-      <c r="H60" s="9">
+      <c r="H60" s="7">
         <v>0.57999999999999996</v>
       </c>
-      <c r="I60" s="9">
+      <c r="I60" s="7">
         <v>0.03</v>
       </c>
       <c r="J60">
         <v>0.73</v>
       </c>
+      <c r="K60">
+        <v>0.78</v>
+      </c>
       <c r="L60">
         <v>0</v>
       </c>
-      <c r="M60" s="4"/>
+      <c r="M60" s="8">
+        <f t="shared" si="1"/>
+        <v>0.65700000000000003</v>
+      </c>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
+      <c r="D61" s="10"/>
       <c r="M61" s="4"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
+      <c r="D62" s="10"/>
       <c r="H62" s="3"/>
       <c r="M62" s="4"/>
     </row>
@@ -3177,28 +3489,28 @@
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
+      <c r="D63" s="10"/>
       <c r="M63" s="4"/>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
+      <c r="D64" s="10"/>
       <c r="M64" s="4"/>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
+      <c r="D65" s="10"/>
       <c r="M65" s="4"/>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
+      <c r="D66" s="10"/>
       <c r="H66" s="3"/>
       <c r="M66" s="4"/>
     </row>
@@ -3206,7 +3518,7 @@
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
+      <c r="D67" s="10"/>
       <c r="H67" s="3"/>
       <c r="M67" s="4"/>
     </row>
@@ -3214,7 +3526,7 @@
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
+      <c r="D68" s="10"/>
       <c r="H68" s="3"/>
       <c r="M68" s="4"/>
     </row>
@@ -3222,7 +3534,7 @@
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
+      <c r="D69" s="10"/>
       <c r="H69" s="3"/>
       <c r="M69" s="4"/>
     </row>
@@ -3230,28 +3542,28 @@
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
+      <c r="D70" s="10"/>
       <c r="M70" s="4"/>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
+      <c r="D71" s="10"/>
       <c r="M71" s="4"/>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
+      <c r="D72" s="10"/>
       <c r="M72" s="4"/>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
+      <c r="D73" s="10"/>
       <c r="H73" s="3"/>
       <c r="M73" s="4"/>
     </row>
@@ -3259,1085 +3571,1085 @@
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
+      <c r="D74" s="10"/>
       <c r="M74" s="4"/>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
+      <c r="D75" s="10"/>
       <c r="M75" s="4"/>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
+      <c r="D76" s="10"/>
       <c r="M76" s="4"/>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
+      <c r="D77" s="10"/>
       <c r="M77" s="4"/>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
+      <c r="D78" s="10"/>
       <c r="M78" s="4"/>
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
+      <c r="D79" s="10"/>
       <c r="M79" s="4"/>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
+      <c r="D80" s="10"/>
       <c r="M80" s="4"/>
     </row>
     <row r="81" spans="1:13">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
+      <c r="D81" s="10"/>
       <c r="M81" s="4"/>
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
+      <c r="D82" s="10"/>
       <c r="M82" s="4"/>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
+      <c r="D83" s="10"/>
       <c r="M83" s="4"/>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
+      <c r="D84" s="10"/>
       <c r="M84" s="4"/>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
+      <c r="D85" s="10"/>
       <c r="M85" s="4"/>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
+      <c r="D86" s="10"/>
       <c r="M86" s="4"/>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
+      <c r="D87" s="10"/>
       <c r="M87" s="4"/>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
+      <c r="D88" s="10"/>
       <c r="M88" s="4"/>
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
+      <c r="D89" s="10"/>
       <c r="M89" s="4"/>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
+      <c r="D90" s="10"/>
       <c r="M90" s="4"/>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
+      <c r="D91" s="10"/>
       <c r="M91" s="4"/>
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
+      <c r="D92" s="10"/>
       <c r="M92" s="4"/>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
+      <c r="D93" s="10"/>
       <c r="M93" s="4"/>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
+      <c r="D94" s="10"/>
       <c r="M94" s="4"/>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
+      <c r="D95" s="10"/>
       <c r="M95" s="4"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
+      <c r="D96" s="10"/>
       <c r="M96" s="4"/>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
+      <c r="D97" s="10"/>
       <c r="M97" s="4"/>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
+      <c r="D98" s="10"/>
       <c r="M98" s="4"/>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
+      <c r="D99" s="10"/>
       <c r="M99" s="4"/>
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
+      <c r="D100" s="10"/>
       <c r="M100" s="4"/>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
+      <c r="D101" s="10"/>
       <c r="M101" s="4"/>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
+      <c r="D102" s="10"/>
       <c r="M102" s="4"/>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
+      <c r="D103" s="10"/>
       <c r="M103" s="4"/>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="6"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
+      <c r="D104" s="10"/>
       <c r="M104" s="4"/>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="6"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
+      <c r="D105" s="10"/>
       <c r="M105" s="4"/>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="6"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
+      <c r="D106" s="10"/>
       <c r="M106" s="4"/>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
+      <c r="D107" s="10"/>
       <c r="M107" s="4"/>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
-      <c r="D108" s="6"/>
+      <c r="D108" s="10"/>
       <c r="M108" s="4"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
+      <c r="D109" s="10"/>
       <c r="M109" s="4"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
+      <c r="D110" s="10"/>
       <c r="M110" s="4"/>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="6"/>
       <c r="B111" s="6"/>
       <c r="C111" s="6"/>
-      <c r="D111" s="6"/>
+      <c r="D111" s="10"/>
       <c r="M111" s="4"/>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="6"/>
       <c r="B112" s="6"/>
       <c r="C112" s="6"/>
-      <c r="D112" s="6"/>
+      <c r="D112" s="10"/>
       <c r="M112" s="4"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="6"/>
       <c r="B113" s="6"/>
       <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
+      <c r="D113" s="10"/>
       <c r="M113" s="4"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="6"/>
       <c r="B114" s="6"/>
       <c r="C114" s="6"/>
-      <c r="D114" s="6"/>
+      <c r="D114" s="10"/>
       <c r="M114" s="4"/>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="6"/>
       <c r="B115" s="6"/>
       <c r="C115" s="6"/>
-      <c r="D115" s="6"/>
+      <c r="D115" s="10"/>
       <c r="M115" s="4"/>
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="6"/>
       <c r="B116" s="6"/>
       <c r="C116" s="6"/>
-      <c r="D116" s="6"/>
+      <c r="D116" s="10"/>
       <c r="M116" s="4"/>
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="6"/>
       <c r="B117" s="6"/>
       <c r="C117" s="6"/>
-      <c r="D117" s="6"/>
+      <c r="D117" s="10"/>
       <c r="M117" s="4"/>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="6"/>
-      <c r="D118" s="6"/>
+      <c r="D118" s="10"/>
       <c r="M118" s="4"/>
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="6"/>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
-      <c r="D119" s="6"/>
+      <c r="D119" s="10"/>
       <c r="M119" s="4"/>
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="6"/>
       <c r="B120" s="6"/>
       <c r="C120" s="6"/>
-      <c r="D120" s="6"/>
+      <c r="D120" s="10"/>
       <c r="M120" s="4"/>
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="6"/>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
-      <c r="D121" s="6"/>
+      <c r="D121" s="10"/>
       <c r="M121" s="4"/>
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="6"/>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
-      <c r="D122" s="6"/>
+      <c r="D122" s="10"/>
       <c r="M122" s="4"/>
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="6"/>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
-      <c r="D123" s="6"/>
+      <c r="D123" s="10"/>
       <c r="M123" s="4"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="6"/>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
-      <c r="D124" s="6"/>
+      <c r="D124" s="10"/>
       <c r="M124" s="4"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="6"/>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
-      <c r="D125" s="6"/>
+      <c r="D125" s="10"/>
       <c r="M125" s="4"/>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="6"/>
       <c r="B126" s="6"/>
       <c r="C126" s="6"/>
-      <c r="D126" s="6"/>
+      <c r="D126" s="10"/>
       <c r="M126" s="4"/>
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="6"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
-      <c r="D127" s="6"/>
+      <c r="D127" s="10"/>
       <c r="M127" s="4"/>
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="6"/>
       <c r="B128" s="6"/>
       <c r="C128" s="6"/>
-      <c r="D128" s="6"/>
+      <c r="D128" s="10"/>
       <c r="M128" s="4"/>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="6"/>
       <c r="B129" s="6"/>
       <c r="C129" s="6"/>
-      <c r="D129" s="6"/>
+      <c r="D129" s="10"/>
       <c r="M129" s="4"/>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="6"/>
       <c r="B130" s="6"/>
       <c r="C130" s="6"/>
-      <c r="D130" s="6"/>
+      <c r="D130" s="10"/>
       <c r="M130" s="4"/>
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="6"/>
       <c r="B131" s="6"/>
       <c r="C131" s="6"/>
-      <c r="D131" s="6"/>
+      <c r="D131" s="10"/>
       <c r="M131" s="4"/>
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="6"/>
       <c r="B132" s="6"/>
       <c r="C132" s="6"/>
-      <c r="D132" s="6"/>
+      <c r="D132" s="10"/>
       <c r="M132" s="4"/>
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="6"/>
       <c r="B133" s="6"/>
       <c r="C133" s="6"/>
-      <c r="D133" s="6"/>
+      <c r="D133" s="10"/>
       <c r="M133" s="4"/>
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="6"/>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
-      <c r="D134" s="6"/>
+      <c r="D134" s="10"/>
       <c r="M134" s="4"/>
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="6"/>
       <c r="B135" s="6"/>
       <c r="C135" s="6"/>
-      <c r="D135" s="6"/>
+      <c r="D135" s="10"/>
       <c r="M135" s="4"/>
     </row>
     <row r="136" spans="1:13">
       <c r="A136" s="6"/>
       <c r="B136" s="6"/>
       <c r="C136" s="6"/>
-      <c r="D136" s="6"/>
+      <c r="D136" s="10"/>
       <c r="M136" s="4"/>
     </row>
     <row r="137" spans="1:13">
       <c r="A137" s="6"/>
       <c r="B137" s="6"/>
       <c r="C137" s="6"/>
-      <c r="D137" s="6"/>
+      <c r="D137" s="10"/>
       <c r="M137" s="4"/>
     </row>
     <row r="138" spans="1:13">
       <c r="A138" s="6"/>
       <c r="B138" s="6"/>
       <c r="C138" s="6"/>
-      <c r="D138" s="6"/>
+      <c r="D138" s="10"/>
       <c r="M138" s="4"/>
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="6"/>
       <c r="B139" s="6"/>
       <c r="C139" s="6"/>
-      <c r="D139" s="6"/>
+      <c r="D139" s="10"/>
       <c r="M139" s="4"/>
     </row>
     <row r="140" spans="1:13">
       <c r="A140" s="6"/>
       <c r="B140" s="6"/>
       <c r="C140" s="6"/>
-      <c r="D140" s="6"/>
+      <c r="D140" s="10"/>
       <c r="M140" s="4"/>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="6"/>
       <c r="B141" s="6"/>
       <c r="C141" s="6"/>
-      <c r="D141" s="6"/>
+      <c r="D141" s="10"/>
       <c r="M141" s="4"/>
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="6"/>
       <c r="B142" s="6"/>
       <c r="C142" s="6"/>
-      <c r="D142" s="6"/>
+      <c r="D142" s="10"/>
       <c r="M142" s="4"/>
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="6"/>
       <c r="B143" s="6"/>
       <c r="C143" s="6"/>
-      <c r="D143" s="6"/>
+      <c r="D143" s="10"/>
       <c r="M143" s="4"/>
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="6"/>
       <c r="B144" s="6"/>
       <c r="C144" s="6"/>
-      <c r="D144" s="6"/>
+      <c r="D144" s="10"/>
       <c r="M144" s="4"/>
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="6"/>
       <c r="B145" s="6"/>
       <c r="C145" s="6"/>
-      <c r="D145" s="6"/>
+      <c r="D145" s="10"/>
       <c r="M145" s="4"/>
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="6"/>
       <c r="B146" s="6"/>
       <c r="C146" s="6"/>
-      <c r="D146" s="6"/>
+      <c r="D146" s="10"/>
       <c r="M146" s="4"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="6"/>
       <c r="B147" s="6"/>
       <c r="C147" s="6"/>
-      <c r="D147" s="6"/>
+      <c r="D147" s="10"/>
       <c r="M147" s="4"/>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="6"/>
       <c r="B148" s="6"/>
       <c r="C148" s="6"/>
-      <c r="D148" s="6"/>
+      <c r="D148" s="10"/>
       <c r="M148" s="4"/>
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="6"/>
       <c r="B149" s="6"/>
       <c r="C149" s="6"/>
-      <c r="D149" s="6"/>
+      <c r="D149" s="10"/>
       <c r="M149" s="4"/>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="6"/>
       <c r="B150" s="6"/>
       <c r="C150" s="6"/>
-      <c r="D150" s="6"/>
+      <c r="D150" s="10"/>
       <c r="M150" s="4"/>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="6"/>
       <c r="B151" s="6"/>
       <c r="C151" s="6"/>
-      <c r="D151" s="6"/>
+      <c r="D151" s="10"/>
       <c r="M151" s="4"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="6"/>
       <c r="B152" s="6"/>
       <c r="C152" s="6"/>
-      <c r="D152" s="6"/>
+      <c r="D152" s="10"/>
       <c r="M152" s="4"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="6"/>
       <c r="B153" s="6"/>
       <c r="C153" s="6"/>
-      <c r="D153" s="6"/>
+      <c r="D153" s="10"/>
       <c r="M153" s="4"/>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="6"/>
       <c r="B154" s="6"/>
       <c r="C154" s="6"/>
-      <c r="D154" s="6"/>
+      <c r="D154" s="10"/>
       <c r="M154" s="4"/>
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="6"/>
       <c r="B155" s="6"/>
       <c r="C155" s="6"/>
-      <c r="D155" s="6"/>
+      <c r="D155" s="10"/>
       <c r="M155" s="4"/>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="6"/>
       <c r="B156" s="6"/>
       <c r="C156" s="6"/>
-      <c r="D156" s="6"/>
+      <c r="D156" s="10"/>
       <c r="M156" s="4"/>
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="6"/>
       <c r="B157" s="6"/>
       <c r="C157" s="6"/>
-      <c r="D157" s="6"/>
+      <c r="D157" s="10"/>
       <c r="M157" s="4"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="6"/>
       <c r="B158" s="6"/>
       <c r="C158" s="6"/>
-      <c r="D158" s="6"/>
+      <c r="D158" s="10"/>
       <c r="M158" s="4"/>
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="6"/>
       <c r="B159" s="6"/>
       <c r="C159" s="6"/>
-      <c r="D159" s="6"/>
+      <c r="D159" s="10"/>
       <c r="M159" s="4"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="6"/>
       <c r="B160" s="6"/>
       <c r="C160" s="6"/>
-      <c r="D160" s="6"/>
+      <c r="D160" s="10"/>
       <c r="M160" s="4"/>
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="6"/>
       <c r="B161" s="6"/>
       <c r="C161" s="6"/>
-      <c r="D161" s="6"/>
+      <c r="D161" s="10"/>
       <c r="M161" s="4"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="6"/>
       <c r="B162" s="6"/>
       <c r="C162" s="6"/>
-      <c r="D162" s="6"/>
+      <c r="D162" s="10"/>
       <c r="M162" s="4"/>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="6"/>
       <c r="B163" s="6"/>
       <c r="C163" s="6"/>
-      <c r="D163" s="6"/>
+      <c r="D163" s="10"/>
       <c r="M163" s="4"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="6"/>
       <c r="B164" s="6"/>
       <c r="C164" s="6"/>
-      <c r="D164" s="6"/>
+      <c r="D164" s="10"/>
       <c r="M164" s="4"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="6"/>
       <c r="B165" s="6"/>
       <c r="C165" s="6"/>
-      <c r="D165" s="6"/>
+      <c r="D165" s="10"/>
       <c r="M165" s="4"/>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="6"/>
       <c r="B166" s="6"/>
       <c r="C166" s="6"/>
-      <c r="D166" s="6"/>
+      <c r="D166" s="10"/>
       <c r="M166" s="4"/>
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="6"/>
       <c r="B167" s="6"/>
       <c r="C167" s="6"/>
-      <c r="D167" s="6"/>
+      <c r="D167" s="10"/>
       <c r="M167" s="4"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="6"/>
       <c r="B168" s="6"/>
       <c r="C168" s="6"/>
-      <c r="D168" s="6"/>
+      <c r="D168" s="10"/>
       <c r="M168" s="4"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="6"/>
       <c r="B169" s="6"/>
       <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
+      <c r="D169" s="10"/>
       <c r="M169" s="4"/>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="6"/>
       <c r="B170" s="6"/>
       <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
+      <c r="D170" s="10"/>
       <c r="M170" s="4"/>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="6"/>
       <c r="B171" s="6"/>
       <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
+      <c r="D171" s="10"/>
       <c r="M171" s="4"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
+      <c r="D172" s="10"/>
       <c r="M172" s="4"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="6"/>
       <c r="B173" s="6"/>
       <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
+      <c r="D173" s="10"/>
       <c r="M173" s="4"/>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="6"/>
       <c r="B174" s="6"/>
       <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
+      <c r="D174" s="10"/>
       <c r="M174" s="4"/>
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="6"/>
       <c r="B175" s="6"/>
       <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
+      <c r="D175" s="10"/>
       <c r="M175" s="4"/>
     </row>
     <row r="176" spans="1:13">
       <c r="A176" s="6"/>
       <c r="B176" s="6"/>
       <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
+      <c r="D176" s="10"/>
       <c r="M176" s="4"/>
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="6"/>
       <c r="B177" s="6"/>
       <c r="C177" s="6"/>
-      <c r="D177" s="6"/>
+      <c r="D177" s="10"/>
       <c r="M177" s="4"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="6"/>
       <c r="B178" s="6"/>
       <c r="C178" s="6"/>
-      <c r="D178" s="6"/>
+      <c r="D178" s="10"/>
       <c r="M178" s="4"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="6"/>
       <c r="B179" s="6"/>
       <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
+      <c r="D179" s="10"/>
       <c r="M179" s="4"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="6"/>
       <c r="B180" s="6"/>
       <c r="C180" s="6"/>
-      <c r="D180" s="6"/>
+      <c r="D180" s="10"/>
       <c r="M180" s="4"/>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="6"/>
-      <c r="D181" s="6"/>
+      <c r="D181" s="10"/>
       <c r="M181" s="4"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="6"/>
       <c r="B182" s="6"/>
       <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
+      <c r="D182" s="10"/>
       <c r="M182" s="4"/>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="6"/>
       <c r="B183" s="6"/>
       <c r="C183" s="6"/>
-      <c r="D183" s="6"/>
+      <c r="D183" s="10"/>
       <c r="M183" s="4"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="6"/>
       <c r="B184" s="6"/>
       <c r="C184" s="6"/>
-      <c r="D184" s="6"/>
+      <c r="D184" s="10"/>
       <c r="M184" s="4"/>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="6"/>
       <c r="B185" s="6"/>
       <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
+      <c r="D185" s="10"/>
       <c r="M185" s="4"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="6"/>
       <c r="B186" s="6"/>
       <c r="C186" s="6"/>
-      <c r="D186" s="6"/>
+      <c r="D186" s="10"/>
       <c r="M186" s="4"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="6"/>
       <c r="B187" s="6"/>
       <c r="C187" s="6"/>
-      <c r="D187" s="6"/>
+      <c r="D187" s="10"/>
       <c r="M187" s="4"/>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="6"/>
       <c r="B188" s="6"/>
       <c r="C188" s="6"/>
-      <c r="D188" s="6"/>
+      <c r="D188" s="10"/>
       <c r="M188" s="4"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="6"/>
       <c r="B189" s="6"/>
       <c r="C189" s="6"/>
-      <c r="D189" s="6"/>
+      <c r="D189" s="10"/>
       <c r="M189" s="4"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="6"/>
       <c r="B190" s="6"/>
       <c r="C190" s="6"/>
-      <c r="D190" s="6"/>
+      <c r="D190" s="10"/>
       <c r="M190" s="4"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="6"/>
       <c r="B191" s="6"/>
       <c r="C191" s="6"/>
-      <c r="D191" s="6"/>
+      <c r="D191" s="10"/>
       <c r="M191" s="4"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="6"/>
       <c r="B192" s="6"/>
       <c r="C192" s="6"/>
-      <c r="D192" s="6"/>
+      <c r="D192" s="10"/>
       <c r="M192" s="4"/>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="6"/>
       <c r="B193" s="6"/>
       <c r="C193" s="6"/>
-      <c r="D193" s="6"/>
+      <c r="D193" s="10"/>
       <c r="M193" s="4"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="6"/>
       <c r="B194" s="6"/>
       <c r="C194" s="6"/>
-      <c r="D194" s="6"/>
+      <c r="D194" s="10"/>
       <c r="M194" s="4"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="6"/>
       <c r="B195" s="6"/>
       <c r="C195" s="6"/>
-      <c r="D195" s="6"/>
+      <c r="D195" s="10"/>
       <c r="M195" s="4"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="6"/>
       <c r="B196" s="6"/>
       <c r="C196" s="6"/>
-      <c r="D196" s="6"/>
+      <c r="D196" s="10"/>
       <c r="M196" s="4"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="6"/>
       <c r="B197" s="6"/>
       <c r="C197" s="6"/>
-      <c r="D197" s="6"/>
+      <c r="D197" s="10"/>
       <c r="M197" s="4"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="6"/>
       <c r="B198" s="6"/>
       <c r="C198" s="6"/>
-      <c r="D198" s="6"/>
+      <c r="D198" s="10"/>
       <c r="M198" s="4"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="6"/>
       <c r="B199" s="6"/>
       <c r="C199" s="6"/>
-      <c r="D199" s="6"/>
+      <c r="D199" s="10"/>
       <c r="M199" s="4"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="6"/>
       <c r="B200" s="6"/>
       <c r="C200" s="6"/>
-      <c r="D200" s="6"/>
+      <c r="D200" s="10"/>
       <c r="M200" s="4"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="6"/>
       <c r="B201" s="6"/>
       <c r="C201" s="6"/>
-      <c r="D201" s="6"/>
+      <c r="D201" s="10"/>
       <c r="M201" s="4"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="6"/>
       <c r="B202" s="6"/>
       <c r="C202" s="6"/>
-      <c r="D202" s="6"/>
+      <c r="D202" s="10"/>
       <c r="M202" s="4"/>
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="6"/>
       <c r="B203" s="6"/>
       <c r="C203" s="6"/>
-      <c r="D203" s="6"/>
+      <c r="D203" s="10"/>
       <c r="M203" s="4"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="6"/>
       <c r="B204" s="6"/>
       <c r="C204" s="6"/>
-      <c r="D204" s="6"/>
+      <c r="D204" s="10"/>
       <c r="M204" s="4"/>
     </row>
     <row r="205" spans="1:13">
       <c r="A205" s="6"/>
       <c r="B205" s="6"/>
       <c r="C205" s="6"/>
-      <c r="D205" s="6"/>
+      <c r="D205" s="10"/>
       <c r="M205" s="4"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="6"/>
       <c r="B206" s="6"/>
       <c r="C206" s="6"/>
-      <c r="D206" s="6"/>
+      <c r="D206" s="10"/>
       <c r="M206" s="4"/>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="6"/>
       <c r="B207" s="6"/>
       <c r="C207" s="6"/>
-      <c r="D207" s="6"/>
+      <c r="D207" s="10"/>
       <c r="M207" s="4"/>
     </row>
     <row r="208" spans="1:13">
       <c r="A208" s="6"/>
       <c r="B208" s="6"/>
       <c r="C208" s="6"/>
-      <c r="D208" s="6"/>
+      <c r="D208" s="10"/>
       <c r="M208" s="4"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="6"/>
       <c r="B209" s="6"/>
       <c r="C209" s="6"/>
-      <c r="D209" s="6"/>
+      <c r="D209" s="10"/>
       <c r="M209" s="4"/>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="6"/>
       <c r="B210" s="6"/>
       <c r="C210" s="6"/>
-      <c r="D210" s="6"/>
+      <c r="D210" s="10"/>
       <c r="M210" s="4"/>
     </row>
     <row r="211" spans="1:13">
       <c r="A211" s="6"/>
       <c r="B211" s="6"/>
       <c r="C211" s="6"/>
-      <c r="D211" s="6"/>
+      <c r="D211" s="10"/>
       <c r="M211" s="4"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="6"/>
       <c r="B212" s="6"/>
       <c r="C212" s="6"/>
-      <c r="D212" s="6"/>
+      <c r="D212" s="10"/>
       <c r="M212" s="4"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="6"/>
       <c r="B213" s="6"/>
       <c r="C213" s="6"/>
-      <c r="D213" s="6"/>
+      <c r="D213" s="10"/>
       <c r="M213" s="4"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="6"/>
       <c r="B214" s="6"/>
       <c r="C214" s="6"/>
-      <c r="D214" s="6"/>
+      <c r="D214" s="10"/>
       <c r="M214" s="4"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="6"/>
       <c r="B215" s="6"/>
       <c r="C215" s="6"/>
-      <c r="D215" s="6"/>
+      <c r="D215" s="10"/>
       <c r="M215" s="4"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="6"/>
       <c r="B216" s="6"/>
       <c r="C216" s="6"/>
-      <c r="D216" s="6"/>
+      <c r="D216" s="10"/>
       <c r="M216" s="4"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="6"/>
       <c r="B217" s="6"/>
       <c r="C217" s="6"/>
-      <c r="D217" s="6"/>
+      <c r="D217" s="10"/>
       <c r="M217" s="4"/>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="6"/>
       <c r="B218" s="6"/>
       <c r="C218" s="6"/>
-      <c r="D218" s="6"/>
+      <c r="D218" s="10"/>
       <c r="M218" s="4"/>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
-      <c r="D219" s="5"/>
+      <c r="D219" s="11"/>
       <c r="M219" s="4"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
-      <c r="D220" s="5"/>
+      <c r="D220" s="11"/>
       <c r="M220" s="4"/>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
-      <c r="D221" s="5"/>
+      <c r="D221" s="11"/>
       <c r="M221" s="4"/>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
-      <c r="D222" s="5"/>
+      <c r="D222" s="11"/>
       <c r="M222" s="4"/>
     </row>
     <row r="223" spans="1:13">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
-      <c r="D223" s="5"/>
+      <c r="D223" s="11"/>
       <c r="M223" s="4"/>
     </row>
     <row r="224" spans="1:13">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
-      <c r="D224" s="5"/>
+      <c r="D224" s="11"/>
       <c r="M224" s="4"/>
     </row>
     <row r="225" spans="1:13">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
-      <c r="D225" s="5"/>
+      <c r="D225" s="11"/>
       <c r="M225" s="4"/>
     </row>
     <row r="226" spans="1:13">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
-      <c r="D226" s="5"/>
+      <c r="D226" s="11"/>
       <c r="M226" s="4"/>
     </row>
     <row r="227" spans="1:13">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
-      <c r="D227" s="5"/>
+      <c r="D227" s="11"/>
       <c r="M227" s="4"/>
     </row>
     <row r="228" spans="1:13">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
-      <c r="D228" s="5"/>
+      <c r="D228" s="11"/>
       <c r="M228" s="4"/>
     </row>
   </sheetData>
